--- a/html-files/DEF_Mondiali_2026_MASTER.xlsx
+++ b/html-files/DEF_Mondiali_2026_MASTER.xlsx
@@ -873,21 +873,21 @@
       </c>
       <c r="I1" s="1">
         <f>SUM(I3:I74)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="1">
         <f>SUM(K3:K74)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="1">
         <f>SUM(M3:M74)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>10</v>
@@ -901,35 +901,35 @@
       </c>
       <c r="Q1" s="1">
         <f>SUM(Q3:Q74)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="S1" s="1">
         <f>SUM(S3:S74)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="U1" s="1">
         <f>SUM(U3:U74)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V1" s="2" t="s">
         <v>14</v>
       </c>
       <c r="W1" s="1">
         <f>SUM(W3:W74)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X1" s="2" t="s">
         <v>15</v>
       </c>
       <c r="Y1" s="1">
         <f>SUM(Y3:Y74)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z1" s="2" t="s">
         <v>16</v>
@@ -950,70 +950,70 @@
       </c>
       <c r="AE1" s="1">
         <f>SUM(AE3:AE74)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF1" s="2" t="s">
         <v>19</v>
       </c>
       <c r="AG1" s="1">
         <f>SUM(AG3:AG74)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH1" s="2" t="s">
         <v>20</v>
       </c>
       <c r="AI1" s="1">
         <f>SUM(AI3:AI74)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ1" s="2" t="s">
         <v>21</v>
       </c>
       <c r="AK1" s="1">
         <f>SUM(AK3:AK74)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL1" s="2" t="s">
         <v>22</v>
       </c>
       <c r="AM1" s="1">
         <f>SUM(AM3:AM74)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN1" s="2" t="s">
         <v>23</v>
       </c>
       <c r="AO1" s="1">
         <f>SUM(AO3:AO74)</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="AQ1" s="1">
         <f>SUM(AQ3:AQ74)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR1" s="2" t="s">
         <v>25</v>
       </c>
       <c r="AS1" s="1">
         <f>SUM(AS3:AS74)</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT1" s="2" t="s">
         <v>26</v>
       </c>
       <c r="AU1" s="1">
         <f>SUM(AU3:AU74)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV1" s="2" t="s">
         <v>27</v>
       </c>
       <c r="AW1" s="1">
         <f>SUM(AW3:AW74)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" ht="21.75" customHeight="1">
@@ -1173,28 +1173,28 @@
         <v>35</v>
       </c>
       <c r="G3" s="5">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H3" s="6">
         <v>1.0</v>
       </c>
       <c r="I3" s="7">
         <f t="shared" ref="I3:I74" si="1">IF($G3&lt;&gt;"",IF(H3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="6">
         <v>1.0</v>
       </c>
       <c r="K3" s="7">
         <f t="shared" ref="K3:K74" si="2">IF($G3&lt;&gt;"",IF(J3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="6">
         <v>1.0</v>
       </c>
       <c r="M3" s="7">
         <f t="shared" ref="M3:M74" si="3">IF($G3&lt;&gt;"",IF(L3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" s="6" t="s">
         <v>36</v>
@@ -1208,35 +1208,35 @@
       </c>
       <c r="Q3" s="7">
         <f t="shared" ref="Q3:Q74" si="5">IF($G3&lt;&gt;"",IF(P3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" s="6">
         <v>1.0</v>
       </c>
       <c r="S3" s="7">
         <f t="shared" ref="S3:S74" si="6">IF($G3&lt;&gt;"",IF(R3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" s="6">
         <v>1.0</v>
       </c>
       <c r="U3" s="7">
         <f t="shared" ref="U3:U74" si="7">IF($G3&lt;&gt;"",IF(T3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="6">
         <v>1.0</v>
       </c>
       <c r="W3" s="7">
         <f t="shared" ref="W3:W74" si="8">IF($G3&lt;&gt;"",IF(V3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" s="6">
         <v>1.0</v>
       </c>
       <c r="Y3" s="7">
         <f t="shared" ref="Y3:Y74" si="9">IF($G3&lt;&gt;"",IF(X3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="6" t="s">
         <v>36</v>
@@ -1257,70 +1257,70 @@
       </c>
       <c r="AE3" s="7">
         <f t="shared" ref="AE3:AE74" si="12">IF($G3&lt;&gt;"",IF(AD3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" s="6">
         <v>2.0</v>
       </c>
       <c r="AG3" s="7">
         <f t="shared" ref="AG3:AG74" si="13">IF($G3&lt;&gt;"",IF(AF3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH3" s="6">
         <v>1.0</v>
       </c>
       <c r="AI3" s="7">
         <f t="shared" ref="AI3:AI74" si="14">IF($G3&lt;&gt;"",IF(AH3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" s="6">
         <v>1.0</v>
       </c>
       <c r="AK3" s="7">
         <f t="shared" ref="AK3:AK74" si="15">IF($G3&lt;&gt;"",IF(AJ3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL3" s="6">
         <v>1.0</v>
       </c>
       <c r="AM3" s="7">
         <f t="shared" ref="AM3:AM74" si="16">IF($G3&lt;&gt;"",IF(AL3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN3" s="6">
         <v>1.0</v>
       </c>
       <c r="AO3" s="7">
         <f t="shared" ref="AO3:AO74" si="17">IF($G3&lt;&gt;"",IF(AN3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP3" s="6">
         <v>1.0</v>
       </c>
       <c r="AQ3" s="7">
         <f t="shared" ref="AQ3:AQ74" si="18">IF($G3&lt;&gt;"",IF(AP3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR3" s="6">
         <v>1.0</v>
       </c>
       <c r="AS3" s="7">
         <f t="shared" ref="AS3:AS74" si="19">IF($G3&lt;&gt;"",IF(AR3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT3" s="6">
         <v>1.0</v>
       </c>
       <c r="AU3" s="7">
         <f t="shared" ref="AU3:AU74" si="20">IF($G3&lt;&gt;"",IF(AT3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV3" s="6">
         <v>1.0</v>
       </c>
       <c r="AW3" s="7">
         <f t="shared" ref="AW3:AW74" si="21">IF($G3&lt;&gt;"",IF(AV3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="18.0" customHeight="1">
@@ -61674,7 +61674,7 @@
       </c>
       <c r="C5" s="19">
         <f>'Previsioni partecipanti'!I1</f>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
@@ -61685,7 +61685,7 @@
       </c>
       <c r="C6" s="19">
         <f>'Previsioni partecipanti'!K1</f>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -61696,7 +61696,7 @@
       </c>
       <c r="C7" s="19">
         <f>'Previsioni partecipanti'!M1</f>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -61718,7 +61718,7 @@
       </c>
       <c r="C9" s="19">
         <f>'Previsioni partecipanti'!Q1</f>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
@@ -61729,7 +61729,7 @@
       </c>
       <c r="C10" s="19">
         <f>'Previsioni partecipanti'!S1</f>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
@@ -61740,7 +61740,7 @@
       </c>
       <c r="C11" s="19">
         <f>'Previsioni partecipanti'!U1</f>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
@@ -61751,7 +61751,7 @@
       </c>
       <c r="C12" s="19">
         <f>'Previsioni partecipanti'!W1</f>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
@@ -61762,7 +61762,7 @@
       </c>
       <c r="C13" s="19">
         <f>'Previsioni partecipanti'!Y1</f>
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
@@ -61795,7 +61795,7 @@
       </c>
       <c r="C16" s="19">
         <f>'Previsioni partecipanti'!AE1</f>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -61806,7 +61806,7 @@
       </c>
       <c r="C17" s="19">
         <f>'Previsioni partecipanti'!AG1</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
@@ -61817,7 +61817,7 @@
       </c>
       <c r="C18" s="19">
         <f>'Previsioni partecipanti'!AI1</f>
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
@@ -61828,7 +61828,7 @@
       </c>
       <c r="C19" s="19">
         <f>'Previsioni partecipanti'!AK1</f>
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -61839,7 +61839,7 @@
       </c>
       <c r="C20" s="19">
         <f>'Previsioni partecipanti'!AM1</f>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
@@ -61850,7 +61850,7 @@
       </c>
       <c r="C21" s="19">
         <f>'Previsioni partecipanti'!AO1</f>
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
@@ -61861,7 +61861,7 @@
       </c>
       <c r="C22" s="19">
         <f>'Previsioni partecipanti'!AQ1</f>
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
@@ -61872,7 +61872,7 @@
       </c>
       <c r="C23" s="19">
         <f>'Previsioni partecipanti'!AS1</f>
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
@@ -61883,7 +61883,7 @@
       </c>
       <c r="C24" s="19">
         <f>'Previsioni partecipanti'!AU1</f>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
@@ -61894,7 +61894,7 @@
       </c>
       <c r="C25" s="19">
         <f>'Previsioni partecipanti'!AW1</f>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
@@ -64873,7 +64873,7 @@
       </c>
       <c r="C3" s="1">
         <f t="array" ref="C3">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B3,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>130</v>
@@ -64889,7 +64889,7 @@
       </c>
       <c r="C4" s="1">
         <f t="array" ref="C4">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B4,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3"/>
     </row>
@@ -64903,7 +64903,7 @@
       </c>
       <c r="C5" s="1">
         <f t="array" ref="C5">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B5,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -64913,11 +64913,11 @@
       </c>
       <c r="B6" s="21" t="str">
         <f t="array" ref="B6">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B5,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,4),1,0),0)),"")</f>
-        <v>Alessio S.</v>
+        <v>Alessandra C.</v>
       </c>
       <c r="C6" s="1">
         <f t="array" ref="C6">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B6,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" s="3"/>
     </row>
@@ -64927,11 +64927,11 @@
       </c>
       <c r="B7" s="21" t="str">
         <f t="array" ref="B7">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B6,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,5),1,0),0)),"")</f>
-        <v>Federico R.</v>
+        <v>Marco G.</v>
       </c>
       <c r="C7" s="1">
         <f t="array" ref="C7">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B7,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" s="1"/>
     </row>
@@ -64941,7 +64941,7 @@
       </c>
       <c r="B8" s="21" t="str">
         <f t="array" ref="B8">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B7,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,6),1,0),0)),"")</f>
-        <v>Alessandra C.</v>
+        <v>Alessio S.</v>
       </c>
       <c r="C8" s="1">
         <f t="array" ref="C8">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B8,Elenco!$B$5:$B$25,0)),"")</f>
@@ -64955,7 +64955,7 @@
       </c>
       <c r="B9" s="21" t="str">
         <f t="array" ref="B9">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B8,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,7),1,0),0)),"")</f>
-        <v>Alessio R.</v>
+        <v>Federico R.</v>
       </c>
       <c r="C9" s="1">
         <f t="array" ref="C9">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B9,Elenco!$B$5:$B$25,0)),"")</f>
@@ -64969,7 +64969,7 @@
       </c>
       <c r="B10" s="21" t="str">
         <f t="array" ref="B10">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B9,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,8),1,0),0)),"")</f>
-        <v>Leo Proietti</v>
+        <v>Alessio R.</v>
       </c>
       <c r="C10" s="1">
         <f t="array" ref="C10">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B10,Elenco!$B$5:$B$25,0)),"")</f>
@@ -64983,11 +64983,11 @@
       </c>
       <c r="B11" s="21" t="str">
         <f t="array" ref="B11">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B10,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,9),1,0),0)),"")</f>
-        <v>Jack</v>
+        <v>Leo Proietti</v>
       </c>
       <c r="C11" s="1">
         <f t="array" ref="C11">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B11,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" s="1"/>
     </row>
@@ -64997,11 +64997,11 @@
       </c>
       <c r="B12" s="21" t="str">
         <f t="array" ref="B12">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B11,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,10),1,0),0)),"")</f>
-        <v>Edoardo</v>
+        <v>Jack</v>
       </c>
       <c r="C12" s="1">
         <f t="array" ref="C12">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B12,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12" s="3"/>
     </row>
@@ -65011,11 +65011,11 @@
       </c>
       <c r="B13" s="21" t="str">
         <f t="array" ref="B13">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B12,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,11),1,0),0)),"")</f>
-        <v>Tania</v>
+        <v>Edoardo</v>
       </c>
       <c r="C13" s="1">
         <f t="array" ref="C13">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B13,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D13" s="1"/>
     </row>
@@ -65025,11 +65025,11 @@
       </c>
       <c r="B14" s="21" t="str">
         <f t="array" ref="B14">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B13,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,12),1,0),0)),"")</f>
-        <v>Marco G.</v>
+        <v>Tania</v>
       </c>
       <c r="C14" s="1">
         <f t="array" ref="C14">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B14,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D14" s="3"/>
     </row>
@@ -65043,7 +65043,7 @@
       </c>
       <c r="C15" s="1">
         <f t="array" ref="C15">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B15,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="1"/>
     </row>
@@ -65053,11 +65053,11 @@
       </c>
       <c r="B16" s="21" t="str">
         <f t="array" ref="B16">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B15,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,14),1,0),0)),"")</f>
-        <v>Claudia A.</v>
+        <v>Alessandra P.</v>
       </c>
       <c r="C16" s="1">
         <f t="array" ref="C16">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B16,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="3"/>
     </row>
@@ -65067,11 +65067,11 @@
       </c>
       <c r="B17" s="21" t="str">
         <f t="array" ref="B17">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B16,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,15),1,0),0)),"")</f>
-        <v>Marco P.</v>
+        <v>Claudia A.</v>
       </c>
       <c r="C17" s="1">
         <f t="array" ref="C17">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B17,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="1"/>
     </row>
@@ -65081,7 +65081,7 @@
       </c>
       <c r="B18" s="21" t="str">
         <f t="array" ref="B18">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B17,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,16),1,0),0)),"")</f>
-        <v>Antonella</v>
+        <v>Marco P.</v>
       </c>
       <c r="C18" s="1">
         <f t="array" ref="C18">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B18,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65095,11 +65095,11 @@
       </c>
       <c r="B19" s="21" t="str">
         <f t="array" ref="B19">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B18,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,17),1,0),0)),"")</f>
-        <v>Samuele</v>
+        <v>Antonella</v>
       </c>
       <c r="C19" s="1">
         <f t="array" ref="C19">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B19,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="1"/>
     </row>
@@ -65109,11 +65109,11 @@
       </c>
       <c r="B20" s="21" t="str">
         <f t="array" ref="B20">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B19,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,18),1,0),0)),"")</f>
-        <v>Alessandra P.</v>
+        <v>Samuele</v>
       </c>
       <c r="C20" s="1">
         <f t="array" ref="C20">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B20,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="3"/>
     </row>
@@ -65127,7 +65127,7 @@
       </c>
       <c r="C21" s="1">
         <f t="array" ref="C21">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B21,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="1"/>
     </row>
@@ -65141,7 +65141,7 @@
       </c>
       <c r="C22" s="1">
         <f t="array" ref="C22">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B22,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="3"/>
     </row>

--- a/html-files/DEF_Mondiali_2026_MASTER.xlsx
+++ b/html-files/DEF_Mondiali_2026_MASTER.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="131">
   <si>
     <t>#</t>
   </si>
@@ -873,42 +873,42 @@
       </c>
       <c r="I1" s="1">
         <f>SUM(I3:I74)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="1">
         <f>SUM(K3:K74)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="1">
         <f>SUM(M3:M74)</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="O1" s="1">
         <f>SUM(O3:O74)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="Q1" s="1">
         <f>SUM(Q3:Q74)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="S1" s="1">
         <f>SUM(S3:S74)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>13</v>
@@ -922,35 +922,35 @@
       </c>
       <c r="W1" s="1">
         <f>SUM(W3:W74)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X1" s="2" t="s">
         <v>15</v>
       </c>
       <c r="Y1" s="1">
         <f>SUM(Y3:Y74)</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="AA1" s="1">
         <f>SUM(AA3:AA74)</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AB1" s="2" t="s">
         <v>17</v>
       </c>
       <c r="AC1" s="1">
         <f>SUM(AC3:AC74)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="AE1" s="1">
         <f>SUM(AE3:AE74)</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AF1" s="2" t="s">
         <v>19</v>
@@ -964,14 +964,14 @@
       </c>
       <c r="AI1" s="1">
         <f>SUM(AI3:AI74)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ1" s="2" t="s">
         <v>21</v>
       </c>
       <c r="AK1" s="1">
         <f>SUM(AK3:AK74)</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AL1" s="2" t="s">
         <v>22</v>
@@ -985,35 +985,35 @@
       </c>
       <c r="AO1" s="1">
         <f>SUM(AO3:AO74)</f>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AP1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="AQ1" s="1">
         <f>SUM(AQ3:AQ74)</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AR1" s="2" t="s">
         <v>25</v>
       </c>
       <c r="AS1" s="1">
         <f>SUM(AS3:AS74)</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT1" s="2" t="s">
         <v>26</v>
       </c>
       <c r="AU1" s="1">
         <f>SUM(AU3:AU74)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AV1" s="2" t="s">
         <v>27</v>
       </c>
       <c r="AW1" s="1">
         <f>SUM(AW3:AW74)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" ht="21.75" customHeight="1">
@@ -1342,15 +1342,15 @@
       <c r="F4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="5">
-        <v>1.0</v>
+      <c r="G4" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="H4" s="6">
         <v>1.0</v>
       </c>
       <c r="I4" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="6">
         <v>2.0</v>
@@ -1378,35 +1378,35 @@
       </c>
       <c r="Q4" s="7">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S4" s="7">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" s="6" t="s">
         <v>36</v>
       </c>
       <c r="U4" s="7">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="6" t="s">
         <v>36</v>
       </c>
       <c r="W4" s="7">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" s="6">
         <v>1.0</v>
       </c>
       <c r="Y4" s="7">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="6">
         <v>2.0</v>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="AC4" s="7">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4" s="6">
         <v>2.0</v>
@@ -1434,42 +1434,42 @@
       </c>
       <c r="AG4" s="7">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4" s="6" t="s">
         <v>36</v>
       </c>
       <c r="AI4" s="7">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" s="6">
         <v>1.0</v>
       </c>
       <c r="AK4" s="7">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL4" s="6">
         <v>1.0</v>
       </c>
       <c r="AM4" s="7">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN4" s="6">
         <v>1.0</v>
       </c>
       <c r="AO4" s="7">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP4" s="6">
         <v>1.0</v>
       </c>
       <c r="AQ4" s="7">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR4" s="6">
         <v>2.0</v>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="AU4" s="7">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV4" s="6">
         <v>2.0</v>
@@ -1513,7 +1513,7 @@
         <v>43</v>
       </c>
       <c r="G5" s="5">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>36</v>
@@ -1541,126 +1541,126 @@
       </c>
       <c r="O5" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" s="6">
         <v>1.0</v>
       </c>
       <c r="Q5" s="7">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" s="6">
         <v>2.0</v>
       </c>
       <c r="S5" s="7">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" s="6">
         <v>1.0</v>
       </c>
       <c r="U5" s="7">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" s="6">
         <v>1.0</v>
       </c>
       <c r="W5" s="7">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" s="6">
         <v>1.0</v>
       </c>
       <c r="Y5" s="7">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="6">
         <v>1.0</v>
       </c>
       <c r="AA5" s="7">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="6">
         <v>1.0</v>
       </c>
       <c r="AC5" s="7">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" s="6">
         <v>1.0</v>
       </c>
       <c r="AE5" s="7">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF5" s="6">
         <v>2.0</v>
       </c>
       <c r="AG5" s="7">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH5" s="6">
         <v>1.0</v>
       </c>
       <c r="AI5" s="7">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="6">
         <v>1.0</v>
       </c>
       <c r="AK5" s="7">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL5" s="6">
         <v>2.0</v>
       </c>
       <c r="AM5" s="7">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN5" s="6">
         <v>1.0</v>
       </c>
       <c r="AO5" s="7">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP5" s="6">
         <v>1.0</v>
       </c>
       <c r="AQ5" s="7">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR5" s="6">
         <v>1.0</v>
       </c>
       <c r="AS5" s="7">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT5" s="6">
         <v>2.0</v>
       </c>
       <c r="AU5" s="7">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV5" s="6">
         <v>2.0</v>
       </c>
       <c r="AW5" s="7">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="18.0" customHeight="1">
@@ -1683,7 +1683,7 @@
         <v>48</v>
       </c>
       <c r="G6" s="5">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>36</v>
@@ -1697,21 +1697,21 @@
       </c>
       <c r="K6" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="6">
         <v>1.0</v>
       </c>
       <c r="M6" s="7">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" s="6">
         <v>1.0</v>
       </c>
       <c r="O6" s="7">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" s="6" t="s">
         <v>36</v>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="S6" s="7">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" s="6" t="s">
         <v>36</v>
@@ -1739,14 +1739,14 @@
       </c>
       <c r="W6" s="7">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6" s="6">
         <v>1.0</v>
       </c>
       <c r="Y6" s="7">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="6" t="s">
         <v>36</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="AE6" s="7">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF6" s="6" t="s">
         <v>49</v>
@@ -1781,14 +1781,14 @@
       </c>
       <c r="AI6" s="7">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" s="6">
         <v>1.0</v>
       </c>
       <c r="AK6" s="7">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL6" s="6" t="s">
         <v>36</v>
@@ -1802,28 +1802,28 @@
       </c>
       <c r="AO6" s="7">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP6" s="6">
         <v>1.0</v>
       </c>
       <c r="AQ6" s="7">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR6" s="6">
         <v>1.0</v>
       </c>
       <c r="AS6" s="7">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT6" s="6">
         <v>2.0</v>
       </c>
       <c r="AU6" s="7">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV6" s="6" t="s">
         <v>36</v>
@@ -1853,84 +1853,84 @@
         <v>51</v>
       </c>
       <c r="G7" s="5">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H7" s="6">
         <v>2.0</v>
       </c>
       <c r="I7" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="6">
         <v>2.0</v>
       </c>
       <c r="K7" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="6">
         <v>1.0</v>
       </c>
       <c r="M7" s="7">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" s="6">
         <v>2.0</v>
       </c>
       <c r="O7" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="6">
         <v>2.0</v>
       </c>
       <c r="Q7" s="7">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="6">
         <v>2.0</v>
       </c>
       <c r="S7" s="7">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" s="6">
         <v>2.0</v>
       </c>
       <c r="U7" s="7">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="6">
         <v>2.0</v>
       </c>
       <c r="W7" s="7">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" s="6">
         <v>2.0</v>
       </c>
       <c r="Y7" s="7">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" s="6">
         <v>1.0</v>
       </c>
       <c r="AA7" s="7">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="6">
         <v>2.0</v>
       </c>
       <c r="AC7" s="7">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" s="6" t="s">
         <v>36</v>
@@ -1944,63 +1944,63 @@
       </c>
       <c r="AG7" s="7">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH7" s="6">
         <v>2.0</v>
       </c>
       <c r="AI7" s="7">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" s="6">
         <v>2.0</v>
       </c>
       <c r="AK7" s="7">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL7" s="6">
         <v>2.0</v>
       </c>
       <c r="AM7" s="7">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN7" s="6">
         <v>2.0</v>
       </c>
       <c r="AO7" s="7">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP7" s="6">
         <v>2.0</v>
       </c>
       <c r="AQ7" s="7">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR7" s="6">
         <v>2.0</v>
       </c>
       <c r="AS7" s="7">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT7" s="6">
         <v>2.0</v>
       </c>
       <c r="AU7" s="7">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV7" s="6">
         <v>2.0</v>
       </c>
       <c r="AW7" s="7">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="18.0" customHeight="1">
@@ -2023,28 +2023,28 @@
         <v>56</v>
       </c>
       <c r="G8" s="5">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H8" s="6">
         <v>1.0</v>
       </c>
       <c r="I8" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="6">
         <v>1.0</v>
       </c>
       <c r="K8" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="6">
         <v>1.0</v>
       </c>
       <c r="M8" s="7">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" s="6" t="s">
         <v>36</v>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="U8" s="7">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="6" t="s">
         <v>36</v>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="AA8" s="7">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="6" t="s">
         <v>36</v>
@@ -2107,21 +2107,21 @@
       </c>
       <c r="AE8" s="7">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="6">
         <v>1.0</v>
       </c>
       <c r="AG8" s="7">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH8" s="6">
         <v>1.0</v>
       </c>
       <c r="AI8" s="7">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" s="6" t="s">
         <v>36</v>
@@ -2142,35 +2142,35 @@
       </c>
       <c r="AO8" s="7">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP8" s="6">
         <v>1.0</v>
       </c>
       <c r="AQ8" s="7">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR8" s="6">
         <v>1.0</v>
       </c>
       <c r="AS8" s="7">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT8" s="6">
         <v>1.0</v>
       </c>
       <c r="AU8" s="7">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV8" s="6">
         <v>1.0</v>
       </c>
       <c r="AW8" s="7">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="18.0" customHeight="1">
@@ -2193,56 +2193,56 @@
         <v>58</v>
       </c>
       <c r="G9" s="5">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H9" s="6">
         <v>2.0</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="6">
         <v>2.0</v>
       </c>
       <c r="K9" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="6">
         <v>2.0</v>
       </c>
       <c r="M9" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="6">
         <v>2.0</v>
       </c>
       <c r="O9" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" s="6">
         <v>2.0</v>
       </c>
       <c r="Q9" s="7">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="6">
         <v>2.0</v>
       </c>
       <c r="S9" s="7">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" s="6">
         <v>2.0</v>
       </c>
       <c r="U9" s="7">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="6" t="s">
         <v>36</v>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="Y9" s="7">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" s="6" t="s">
         <v>36</v>
@@ -2270,28 +2270,28 @@
       </c>
       <c r="AC9" s="7">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD9" s="6">
         <v>2.0</v>
       </c>
       <c r="AE9" s="7">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" s="6">
         <v>2.0</v>
       </c>
       <c r="AG9" s="7">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH9" s="6">
         <v>2.0</v>
       </c>
       <c r="AI9" s="7">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" s="6" t="s">
         <v>36</v>
@@ -2312,35 +2312,35 @@
       </c>
       <c r="AO9" s="7">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP9" s="6">
         <v>2.0</v>
       </c>
       <c r="AQ9" s="7">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR9" s="6">
         <v>2.0</v>
       </c>
       <c r="AS9" s="7">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT9" s="6">
         <v>2.0</v>
       </c>
       <c r="AU9" s="7">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV9" s="6">
         <v>2.0</v>
       </c>
       <c r="AW9" s="7">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="18.0" customHeight="1">
@@ -2532,155 +2532,155 @@
       <c r="F11" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="5">
-        <v>1.0</v>
+      <c r="G11" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="H11" s="6">
         <v>1.0</v>
       </c>
       <c r="I11" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="6">
         <v>1.0</v>
       </c>
       <c r="K11" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="6">
         <v>1.0</v>
       </c>
       <c r="M11" s="7">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" s="6">
         <v>1.0</v>
       </c>
       <c r="O11" s="7">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" s="6">
         <v>1.0</v>
       </c>
       <c r="Q11" s="7">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" s="6">
         <v>1.0</v>
       </c>
       <c r="S11" s="7">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" s="6">
         <v>1.0</v>
       </c>
       <c r="U11" s="7">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="6">
         <v>1.0</v>
       </c>
       <c r="W11" s="7">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X11" s="6">
         <v>1.0</v>
       </c>
       <c r="Y11" s="7">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="6">
         <v>1.0</v>
       </c>
       <c r="AA11" s="7">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB11" s="6">
         <v>1.0</v>
       </c>
       <c r="AC11" s="7">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="6">
         <v>1.0</v>
       </c>
       <c r="AE11" s="7">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF11" s="6">
         <v>1.0</v>
       </c>
       <c r="AG11" s="7">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH11" s="6">
         <v>1.0</v>
       </c>
       <c r="AI11" s="7">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" s="6">
         <v>1.0</v>
       </c>
       <c r="AK11" s="7">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL11" s="6">
         <v>1.0</v>
       </c>
       <c r="AM11" s="7">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN11" s="6">
         <v>1.0</v>
       </c>
       <c r="AO11" s="7">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP11" s="6">
         <v>1.0</v>
       </c>
       <c r="AQ11" s="7">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR11" s="6">
         <v>1.0</v>
       </c>
       <c r="AS11" s="7">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT11" s="6">
         <v>1.0</v>
       </c>
       <c r="AU11" s="7">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV11" s="6">
         <v>1.0</v>
       </c>
       <c r="AW11" s="7">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="18.0" customHeight="1">
@@ -4572,153 +4572,155 @@
       <c r="F23" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="G23" s="8"/>
+      <c r="G23" s="5" t="s">
+        <v>36</v>
+      </c>
       <c r="H23" s="6">
         <v>1.0</v>
       </c>
-      <c r="I23" s="7" t="str">
+      <c r="I23" s="7">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J23" s="6">
         <v>1.0</v>
       </c>
-      <c r="K23" s="7" t="str">
+      <c r="K23" s="7">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L23" s="6">
         <v>1.0</v>
       </c>
-      <c r="M23" s="7" t="str">
+      <c r="M23" s="7">
         <f t="shared" si="3"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N23" s="6">
         <v>1.0</v>
       </c>
-      <c r="O23" s="7" t="str">
+      <c r="O23" s="7">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P23" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q23" s="7" t="str">
+      <c r="Q23" s="7">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R23" s="6">
         <v>1.0</v>
       </c>
-      <c r="S23" s="7" t="str">
+      <c r="S23" s="7">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T23" s="6">
         <v>1.0</v>
       </c>
-      <c r="U23" s="7" t="str">
+      <c r="U23" s="7">
         <f t="shared" si="7"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="V23" s="6">
         <v>1.0</v>
       </c>
-      <c r="W23" s="7" t="str">
+      <c r="W23" s="7">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X23" s="6">
         <v>1.0</v>
       </c>
-      <c r="Y23" s="7" t="str">
+      <c r="Y23" s="7">
         <f t="shared" si="9"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Z23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AA23" s="7" t="str">
+      <c r="AA23" s="7">
         <f t="shared" si="10"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AB23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AC23" s="7" t="str">
+      <c r="AC23" s="7">
         <f t="shared" si="11"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AE23" s="7" t="str">
+      <c r="AE23" s="7">
         <f t="shared" si="12"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AG23" s="7" t="str">
+      <c r="AG23" s="7">
         <f t="shared" si="13"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AH23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AI23" s="7" t="str">
+      <c r="AI23" s="7">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AJ23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AK23" s="7" t="str">
+      <c r="AK23" s="7">
         <f t="shared" si="15"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AM23" s="7" t="str">
+      <c r="AM23" s="7">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AN23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO23" s="7" t="str">
+      <c r="AO23" s="7">
         <f t="shared" si="17"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AP23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AQ23" s="7" t="str">
+      <c r="AQ23" s="7">
         <f t="shared" si="18"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AR23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AS23" s="7" t="str">
+      <c r="AS23" s="7">
         <f t="shared" si="19"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AU23" s="7" t="str">
+      <c r="AU23" s="7">
         <f t="shared" si="20"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AV23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AW23" s="7" t="str">
+      <c r="AW23" s="7">
         <f t="shared" si="21"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="24" ht="18.0" customHeight="1">
@@ -61674,7 +61676,7 @@
       </c>
       <c r="C5" s="19">
         <f>'Previsioni partecipanti'!I1</f>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
@@ -61685,7 +61687,7 @@
       </c>
       <c r="C6" s="19">
         <f>'Previsioni partecipanti'!K1</f>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -61696,7 +61698,7 @@
       </c>
       <c r="C7" s="19">
         <f>'Previsioni partecipanti'!M1</f>
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -61707,7 +61709,7 @@
       </c>
       <c r="C8" s="19">
         <f>'Previsioni partecipanti'!O1</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
@@ -61718,7 +61720,7 @@
       </c>
       <c r="C9" s="19">
         <f>'Previsioni partecipanti'!Q1</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
@@ -61729,7 +61731,7 @@
       </c>
       <c r="C10" s="19">
         <f>'Previsioni partecipanti'!S1</f>
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
@@ -61751,7 +61753,7 @@
       </c>
       <c r="C12" s="19">
         <f>'Previsioni partecipanti'!W1</f>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
@@ -61762,7 +61764,7 @@
       </c>
       <c r="C13" s="19">
         <f>'Previsioni partecipanti'!Y1</f>
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
@@ -61773,7 +61775,7 @@
       </c>
       <c r="C14" s="19">
         <f>'Previsioni partecipanti'!AA1</f>
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
@@ -61784,7 +61786,7 @@
       </c>
       <c r="C15" s="19">
         <f>'Previsioni partecipanti'!AC1</f>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
@@ -61795,7 +61797,7 @@
       </c>
       <c r="C16" s="19">
         <f>'Previsioni partecipanti'!AE1</f>
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -61817,7 +61819,7 @@
       </c>
       <c r="C18" s="19">
         <f>'Previsioni partecipanti'!AI1</f>
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
@@ -61828,7 +61830,7 @@
       </c>
       <c r="C19" s="19">
         <f>'Previsioni partecipanti'!AK1</f>
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -61850,7 +61852,7 @@
       </c>
       <c r="C21" s="19">
         <f>'Previsioni partecipanti'!AO1</f>
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
@@ -61861,7 +61863,7 @@
       </c>
       <c r="C22" s="19">
         <f>'Previsioni partecipanti'!AQ1</f>
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
@@ -61872,7 +61874,7 @@
       </c>
       <c r="C23" s="19">
         <f>'Previsioni partecipanti'!AS1</f>
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
@@ -61883,7 +61885,7 @@
       </c>
       <c r="C24" s="19">
         <f>'Previsioni partecipanti'!AU1</f>
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
@@ -61894,7 +61896,7 @@
       </c>
       <c r="C25" s="19">
         <f>'Previsioni partecipanti'!AW1</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
@@ -64869,11 +64871,11 @@
       </c>
       <c r="B3" s="21" t="str">
         <f t="array" ref="B3">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B2,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,1),1,0),0)),"")</f>
-        <v>Khawla</v>
+        <v>Marco G.</v>
       </c>
       <c r="C3" s="1">
         <f t="array" ref="C3">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B3,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>130</v>
@@ -64885,11 +64887,11 @@
       </c>
       <c r="B4" s="21" t="str">
         <f t="array" ref="B4">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B3,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,2),1,0),0)),"")</f>
-        <v>Claudia S.</v>
+        <v>Valerio</v>
       </c>
       <c r="C4" s="1">
         <f t="array" ref="C4">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B4,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3"/>
     </row>
@@ -64899,11 +64901,11 @@
       </c>
       <c r="B5" s="21" t="str">
         <f t="array" ref="B5">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B4,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,3),1,0),0)),"")</f>
-        <v>Pier</v>
+        <v>Alessio S.</v>
       </c>
       <c r="C5" s="1">
         <f t="array" ref="C5">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B5,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -64913,11 +64915,11 @@
       </c>
       <c r="B6" s="21" t="str">
         <f t="array" ref="B6">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B5,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,4),1,0),0)),"")</f>
-        <v>Alessandra C.</v>
+        <v>Claudia S.</v>
       </c>
       <c r="C6" s="1">
         <f t="array" ref="C6">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B6,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6" s="3"/>
     </row>
@@ -64927,11 +64929,11 @@
       </c>
       <c r="B7" s="21" t="str">
         <f t="array" ref="B7">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B6,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,5),1,0),0)),"")</f>
-        <v>Marco G.</v>
+        <v>Leo Policella</v>
       </c>
       <c r="C7" s="1">
         <f t="array" ref="C7">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B7,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" s="1"/>
     </row>
@@ -64941,11 +64943,11 @@
       </c>
       <c r="B8" s="21" t="str">
         <f t="array" ref="B8">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B7,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,6),1,0),0)),"")</f>
-        <v>Alessio S.</v>
+        <v>Edoardo</v>
       </c>
       <c r="C8" s="1">
         <f t="array" ref="C8">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B8,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D8" s="3"/>
     </row>
@@ -64955,11 +64957,11 @@
       </c>
       <c r="B9" s="21" t="str">
         <f t="array" ref="B9">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B8,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,7),1,0),0)),"")</f>
-        <v>Federico R.</v>
+        <v>Pier</v>
       </c>
       <c r="C9" s="1">
         <f t="array" ref="C9">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B9,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D9" s="1"/>
     </row>
@@ -64969,11 +64971,11 @@
       </c>
       <c r="B10" s="21" t="str">
         <f t="array" ref="B10">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B9,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,8),1,0),0)),"")</f>
-        <v>Alessio R.</v>
+        <v>Khawla</v>
       </c>
       <c r="C10" s="1">
         <f t="array" ref="C10">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B10,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D10" s="3"/>
     </row>
@@ -64987,7 +64989,7 @@
       </c>
       <c r="C11" s="1">
         <f t="array" ref="C11">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B11,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="1"/>
     </row>
@@ -65001,7 +65003,7 @@
       </c>
       <c r="C12" s="1">
         <f t="array" ref="C12">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B12,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="3"/>
     </row>
@@ -65011,11 +65013,11 @@
       </c>
       <c r="B13" s="21" t="str">
         <f t="array" ref="B13">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B12,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,11),1,0),0)),"")</f>
-        <v>Edoardo</v>
+        <v>Samuele</v>
       </c>
       <c r="C13" s="1">
         <f t="array" ref="C13">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B13,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="1"/>
     </row>
@@ -65029,7 +65031,7 @@
       </c>
       <c r="C14" s="1">
         <f t="array" ref="C14">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B14,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="3"/>
     </row>
@@ -65039,7 +65041,7 @@
       </c>
       <c r="B15" s="21" t="str">
         <f t="array" ref="B15">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B14,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,13),1,0),0)),"")</f>
-        <v>Valerio</v>
+        <v>Marco P.</v>
       </c>
       <c r="C15" s="1">
         <f t="array" ref="C15">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B15,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65053,7 +65055,7 @@
       </c>
       <c r="B16" s="21" t="str">
         <f t="array" ref="B16">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B15,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,14),1,0),0)),"")</f>
-        <v>Alessandra P.</v>
+        <v>Federico R.</v>
       </c>
       <c r="C16" s="1">
         <f t="array" ref="C16">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B16,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65067,7 +65069,7 @@
       </c>
       <c r="B17" s="21" t="str">
         <f t="array" ref="B17">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B16,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,15),1,0),0)),"")</f>
-        <v>Claudia A.</v>
+        <v>Maila</v>
       </c>
       <c r="C17" s="1">
         <f t="array" ref="C17">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B17,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65081,11 +65083,11 @@
       </c>
       <c r="B18" s="21" t="str">
         <f t="array" ref="B18">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B17,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,16),1,0),0)),"")</f>
-        <v>Marco P.</v>
+        <v>Alessandra C.</v>
       </c>
       <c r="C18" s="1">
         <f t="array" ref="C18">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B18,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="3"/>
     </row>
@@ -65095,7 +65097,7 @@
       </c>
       <c r="B19" s="21" t="str">
         <f t="array" ref="B19">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B18,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,17),1,0),0)),"")</f>
-        <v>Antonella</v>
+        <v>Alessandra P.</v>
       </c>
       <c r="C19" s="1">
         <f t="array" ref="C19">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B19,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65109,7 +65111,7 @@
       </c>
       <c r="B20" s="21" t="str">
         <f t="array" ref="B20">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B19,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,18),1,0),0)),"")</f>
-        <v>Samuele</v>
+        <v>Alessio R.</v>
       </c>
       <c r="C20" s="1">
         <f t="array" ref="C20">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B20,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65123,11 +65125,11 @@
       </c>
       <c r="B21" s="21" t="str">
         <f t="array" ref="B21">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B20,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,19),1,0),0)),"")</f>
-        <v>Leo Policella</v>
+        <v>Vito</v>
       </c>
       <c r="C21" s="1">
         <f t="array" ref="C21">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B21,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D21" s="1"/>
     </row>
@@ -65137,11 +65139,11 @@
       </c>
       <c r="B22" s="21" t="str">
         <f t="array" ref="B22">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B21,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,20),1,0),0)),"")</f>
-        <v>Maila</v>
+        <v>Claudia A.</v>
       </c>
       <c r="C22" s="1">
         <f t="array" ref="C22">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B22,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D22" s="3"/>
     </row>
@@ -65151,11 +65153,11 @@
       </c>
       <c r="B23" s="21" t="str">
         <f t="array" ref="B23">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B22,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,21),1,0),0)),"")</f>
-        <v>Vito</v>
+        <v>Antonella</v>
       </c>
       <c r="C23" s="1">
         <f t="array" ref="C23">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B23,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D23" s="1"/>
     </row>

--- a/html-files/DEF_Mondiali_2026_MASTER.xlsx
+++ b/html-files/DEF_Mondiali_2026_MASTER.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="131">
   <si>
     <t>#</t>
   </si>
@@ -880,7 +880,7 @@
       </c>
       <c r="K1" s="1">
         <f>SUM(K3:K74)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>9</v>
@@ -894,42 +894,42 @@
       </c>
       <c r="O1" s="1">
         <f>SUM(O3:O74)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="Q1" s="1">
         <f>SUM(Q3:Q74)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="S1" s="1">
         <f>SUM(S3:S74)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="U1" s="1">
         <f>SUM(U3:U74)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V1" s="2" t="s">
         <v>14</v>
       </c>
       <c r="W1" s="1">
         <f>SUM(W3:W74)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X1" s="2" t="s">
         <v>15</v>
       </c>
       <c r="Y1" s="1">
         <f>SUM(Y3:Y74)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z1" s="2" t="s">
         <v>16</v>
@@ -943,7 +943,7 @@
       </c>
       <c r="AC1" s="1">
         <f>SUM(AC3:AC74)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD1" s="2" t="s">
         <v>18</v>
@@ -957,7 +957,7 @@
       </c>
       <c r="AG1" s="1">
         <f>SUM(AG3:AG74)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH1" s="2" t="s">
         <v>20</v>
@@ -971,21 +971,21 @@
       </c>
       <c r="AK1" s="1">
         <f>SUM(AK3:AK74)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL1" s="2" t="s">
         <v>22</v>
       </c>
       <c r="AM1" s="1">
         <f>SUM(AM3:AM74)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN1" s="2" t="s">
         <v>23</v>
       </c>
       <c r="AO1" s="1">
         <f>SUM(AO3:AO74)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AP1" s="2" t="s">
         <v>24</v>
@@ -1006,14 +1006,14 @@
       </c>
       <c r="AU1" s="1">
         <f>SUM(AU3:AU74)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV1" s="2" t="s">
         <v>27</v>
       </c>
       <c r="AW1" s="1">
         <f>SUM(AW3:AW74)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" ht="21.75" customHeight="1">
@@ -4742,153 +4742,155 @@
       <c r="F24" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="G24" s="8"/>
+      <c r="G24" s="5" t="s">
+        <v>36</v>
+      </c>
       <c r="H24" s="6">
         <v>1.0</v>
       </c>
-      <c r="I24" s="7" t="str">
+      <c r="I24" s="7">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J24" s="6">
         <v>1.0</v>
       </c>
-      <c r="K24" s="7" t="str">
+      <c r="K24" s="7">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L24" s="6">
         <v>1.0</v>
       </c>
-      <c r="M24" s="7" t="str">
+      <c r="M24" s="7">
         <f t="shared" si="3"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="O24" s="7" t="str">
+      <c r="O24" s="7">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="Q24" s="7" t="str">
+      <c r="Q24" s="7">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="R24" s="6">
         <v>1.0</v>
       </c>
-      <c r="S24" s="7" t="str">
+      <c r="S24" s="7">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T24" s="6">
         <v>1.0</v>
       </c>
-      <c r="U24" s="7" t="str">
+      <c r="U24" s="7">
         <f t="shared" si="7"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="V24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="W24" s="7" t="str">
+      <c r="W24" s="7">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="X24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="Y24" s="7" t="str">
+      <c r="Y24" s="7">
         <f t="shared" si="9"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Z24" s="6">
         <v>1.0</v>
       </c>
-      <c r="AA24" s="7" t="str">
+      <c r="AA24" s="7">
         <f t="shared" si="10"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AB24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AC24" s="7" t="str">
+      <c r="AC24" s="7">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD24" s="6">
         <v>1.0</v>
       </c>
-      <c r="AE24" s="7" t="str">
+      <c r="AE24" s="7">
         <f t="shared" si="12"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF24" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AG24" s="7" t="str">
+      <c r="AG24" s="7">
         <f t="shared" si="13"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AH24" s="6">
         <v>1.0</v>
       </c>
-      <c r="AI24" s="7" t="str">
+      <c r="AI24" s="7">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AJ24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AK24" s="7" t="str">
+      <c r="AK24" s="7">
         <f t="shared" si="15"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AL24" s="6">
         <v>2.0</v>
       </c>
-      <c r="AM24" s="7" t="str">
+      <c r="AM24" s="7">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AN24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AO24" s="7" t="str">
+      <c r="AO24" s="7">
         <f t="shared" si="17"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AP24" s="6">
         <v>1.0</v>
       </c>
-      <c r="AQ24" s="7" t="str">
+      <c r="AQ24" s="7">
         <f t="shared" si="18"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AR24" s="6">
         <v>1.0</v>
       </c>
-      <c r="AS24" s="7" t="str">
+      <c r="AS24" s="7">
         <f t="shared" si="19"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT24" s="6">
         <v>1.0</v>
       </c>
-      <c r="AU24" s="7" t="str">
+      <c r="AU24" s="7">
         <f t="shared" si="20"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AV24" s="6">
         <v>1.0</v>
       </c>
-      <c r="AW24" s="7" t="str">
+      <c r="AW24" s="7">
         <f t="shared" si="21"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="25" ht="18.0" customHeight="1">
@@ -4910,153 +4912,155 @@
       <c r="F25" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="G25" s="8"/>
+      <c r="G25" s="5">
+        <v>1.0</v>
+      </c>
       <c r="H25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I25" s="7" t="str">
+      <c r="I25" s="7">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J25" s="6">
         <v>1.0</v>
       </c>
-      <c r="K25" s="7" t="str">
+      <c r="K25" s="7">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M25" s="7" t="str">
+      <c r="M25" s="7">
         <f t="shared" si="3"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N25" s="6">
         <v>1.0</v>
       </c>
-      <c r="O25" s="7" t="str">
+      <c r="O25" s="7">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="P25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="Q25" s="7" t="str">
+      <c r="Q25" s="7">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R25" s="6">
         <v>1.0</v>
       </c>
-      <c r="S25" s="7" t="str">
+      <c r="S25" s="7">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T25" s="6">
         <v>1.0</v>
       </c>
-      <c r="U25" s="7" t="str">
+      <c r="U25" s="7">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="V25" s="6">
         <v>1.0</v>
       </c>
-      <c r="W25" s="7" t="str">
+      <c r="W25" s="7">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="X25" s="6">
         <v>1.0</v>
       </c>
-      <c r="Y25" s="7" t="str">
+      <c r="Y25" s="7">
         <f t="shared" si="9"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Z25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AA25" s="7" t="str">
+      <c r="AA25" s="7">
         <f t="shared" si="10"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AB25" s="6">
         <v>1.0</v>
       </c>
-      <c r="AC25" s="7" t="str">
+      <c r="AC25" s="7">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AE25" s="7" t="str">
+      <c r="AE25" s="7">
         <f t="shared" si="12"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF25" s="6">
         <v>2.0</v>
       </c>
-      <c r="AG25" s="7" t="str">
+      <c r="AG25" s="7">
         <f t="shared" si="13"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AH25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AI25" s="7" t="str">
+      <c r="AI25" s="7">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AJ25" s="6">
         <v>1.0</v>
       </c>
-      <c r="AK25" s="7" t="str">
+      <c r="AK25" s="7">
         <f t="shared" si="15"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AL25" s="6">
         <v>1.0</v>
       </c>
-      <c r="AM25" s="7" t="str">
+      <c r="AM25" s="7">
         <f t="shared" si="16"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AN25" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO25" s="7" t="str">
+      <c r="AO25" s="7">
         <f t="shared" si="17"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AP25" s="6">
         <v>2.0</v>
       </c>
-      <c r="AQ25" s="7" t="str">
+      <c r="AQ25" s="7">
         <f t="shared" si="18"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AR25" s="6">
         <v>2.0</v>
       </c>
-      <c r="AS25" s="7" t="str">
+      <c r="AS25" s="7">
         <f t="shared" si="19"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT25" s="6">
         <v>1.0</v>
       </c>
-      <c r="AU25" s="7" t="str">
+      <c r="AU25" s="7">
         <f t="shared" si="20"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AV25" s="6">
         <v>1.0</v>
       </c>
-      <c r="AW25" s="7" t="str">
+      <c r="AW25" s="7">
         <f t="shared" si="21"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="26" ht="18.0" customHeight="1">
@@ -61687,7 +61691,7 @@
       </c>
       <c r="C6" s="19">
         <f>'Previsioni partecipanti'!K1</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -61709,7 +61713,7 @@
       </c>
       <c r="C8" s="19">
         <f>'Previsioni partecipanti'!O1</f>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
@@ -61720,7 +61724,7 @@
       </c>
       <c r="C9" s="19">
         <f>'Previsioni partecipanti'!Q1</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
@@ -61731,7 +61735,7 @@
       </c>
       <c r="C10" s="19">
         <f>'Previsioni partecipanti'!S1</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
@@ -61742,7 +61746,7 @@
       </c>
       <c r="C11" s="19">
         <f>'Previsioni partecipanti'!U1</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
@@ -61753,7 +61757,7 @@
       </c>
       <c r="C12" s="19">
         <f>'Previsioni partecipanti'!W1</f>
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
@@ -61764,7 +61768,7 @@
       </c>
       <c r="C13" s="19">
         <f>'Previsioni partecipanti'!Y1</f>
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
@@ -61786,7 +61790,7 @@
       </c>
       <c r="C15" s="19">
         <f>'Previsioni partecipanti'!AC1</f>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
@@ -61808,7 +61812,7 @@
       </c>
       <c r="C17" s="19">
         <f>'Previsioni partecipanti'!AG1</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
@@ -61830,7 +61834,7 @@
       </c>
       <c r="C19" s="19">
         <f>'Previsioni partecipanti'!AK1</f>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -61841,7 +61845,7 @@
       </c>
       <c r="C20" s="19">
         <f>'Previsioni partecipanti'!AM1</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
@@ -61852,7 +61856,7 @@
       </c>
       <c r="C21" s="19">
         <f>'Previsioni partecipanti'!AO1</f>
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
@@ -61885,7 +61889,7 @@
       </c>
       <c r="C24" s="19">
         <f>'Previsioni partecipanti'!AU1</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
@@ -61896,7 +61900,7 @@
       </c>
       <c r="C25" s="19">
         <f>'Previsioni partecipanti'!AW1</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
@@ -64875,7 +64879,7 @@
       </c>
       <c r="C3" s="1">
         <f t="array" ref="C3">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B3,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>130</v>
@@ -64891,7 +64895,7 @@
       </c>
       <c r="C4" s="1">
         <f t="array" ref="C4">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B4,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3"/>
     </row>
@@ -64901,11 +64905,11 @@
       </c>
       <c r="B5" s="21" t="str">
         <f t="array" ref="B5">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B4,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,3),1,0),0)),"")</f>
-        <v>Alessio S.</v>
+        <v>Pier</v>
       </c>
       <c r="C5" s="1">
         <f t="array" ref="C5">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B5,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -64915,11 +64919,11 @@
       </c>
       <c r="B6" s="21" t="str">
         <f t="array" ref="B6">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B5,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,4),1,0),0)),"")</f>
-        <v>Claudia S.</v>
+        <v>Khawla</v>
       </c>
       <c r="C6" s="1">
         <f t="array" ref="C6">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B6,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="3"/>
     </row>
@@ -64933,7 +64937,7 @@
       </c>
       <c r="C7" s="1">
         <f t="array" ref="C7">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B7,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" s="1"/>
     </row>
@@ -64947,7 +64951,7 @@
       </c>
       <c r="C8" s="1">
         <f t="array" ref="C8">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B8,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" s="3"/>
     </row>
@@ -64957,11 +64961,11 @@
       </c>
       <c r="B9" s="21" t="str">
         <f t="array" ref="B9">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B8,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,7),1,0),0)),"")</f>
-        <v>Pier</v>
+        <v>Tania</v>
       </c>
       <c r="C9" s="1">
         <f t="array" ref="C9">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B9,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" s="1"/>
     </row>
@@ -64971,11 +64975,11 @@
       </c>
       <c r="B10" s="21" t="str">
         <f t="array" ref="B10">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B9,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,8),1,0),0)),"")</f>
-        <v>Khawla</v>
+        <v>Alessio S.</v>
       </c>
       <c r="C10" s="1">
         <f t="array" ref="C10">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B10,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="3"/>
     </row>
@@ -64985,11 +64989,11 @@
       </c>
       <c r="B11" s="21" t="str">
         <f t="array" ref="B11">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B10,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,9),1,0),0)),"")</f>
-        <v>Leo Proietti</v>
+        <v>Claudia S.</v>
       </c>
       <c r="C11" s="1">
         <f t="array" ref="C11">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B11,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D11" s="1"/>
     </row>
@@ -65003,7 +65007,7 @@
       </c>
       <c r="C12" s="1">
         <f t="array" ref="C12">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B12,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="3"/>
     </row>
@@ -65017,7 +65021,7 @@
       </c>
       <c r="C13" s="1">
         <f t="array" ref="C13">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B13,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="1"/>
     </row>
@@ -65027,11 +65031,11 @@
       </c>
       <c r="B14" s="21" t="str">
         <f t="array" ref="B14">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B13,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,12),1,0),0)),"")</f>
-        <v>Tania</v>
+        <v>Alessandra P.</v>
       </c>
       <c r="C14" s="1">
         <f t="array" ref="C14">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B14,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="3"/>
     </row>
@@ -65041,11 +65045,11 @@
       </c>
       <c r="B15" s="21" t="str">
         <f t="array" ref="B15">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B14,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,13),1,0),0)),"")</f>
-        <v>Marco P.</v>
+        <v>Alessio R.</v>
       </c>
       <c r="C15" s="1">
         <f t="array" ref="C15">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B15,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="1"/>
     </row>
@@ -65055,11 +65059,11 @@
       </c>
       <c r="B16" s="21" t="str">
         <f t="array" ref="B16">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B15,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,14),1,0),0)),"")</f>
-        <v>Federico R.</v>
+        <v>Marco P.</v>
       </c>
       <c r="C16" s="1">
         <f t="array" ref="C16">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B16,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="3"/>
     </row>
@@ -65073,7 +65077,7 @@
       </c>
       <c r="C17" s="1">
         <f t="array" ref="C17">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B17,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="1"/>
     </row>
@@ -65083,11 +65087,11 @@
       </c>
       <c r="B18" s="21" t="str">
         <f t="array" ref="B18">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B17,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,16),1,0),0)),"")</f>
-        <v>Alessandra C.</v>
+        <v>Leo Proietti</v>
       </c>
       <c r="C18" s="1">
         <f t="array" ref="C18">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B18,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="3"/>
     </row>
@@ -65097,11 +65101,11 @@
       </c>
       <c r="B19" s="21" t="str">
         <f t="array" ref="B19">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B18,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,17),1,0),0)),"")</f>
-        <v>Alessandra P.</v>
+        <v>Vito</v>
       </c>
       <c r="C19" s="1">
         <f t="array" ref="C19">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B19,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="1"/>
     </row>
@@ -65111,11 +65115,11 @@
       </c>
       <c r="B20" s="21" t="str">
         <f t="array" ref="B20">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B19,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,18),1,0),0)),"")</f>
-        <v>Alessio R.</v>
+        <v>Federico R.</v>
       </c>
       <c r="C20" s="1">
         <f t="array" ref="C20">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B20,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="3"/>
     </row>
@@ -65125,11 +65129,11 @@
       </c>
       <c r="B21" s="21" t="str">
         <f t="array" ref="B21">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B20,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,19),1,0),0)),"")</f>
-        <v>Vito</v>
+        <v>Alessandra C.</v>
       </c>
       <c r="C21" s="1">
         <f t="array" ref="C21">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B21,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D21" s="1"/>
     </row>

--- a/html-files/DEF_Mondiali_2026_MASTER.xlsx
+++ b/html-files/DEF_Mondiali_2026_MASTER.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="131">
   <si>
     <t>#</t>
   </si>
@@ -873,147 +873,147 @@
       </c>
       <c r="I1" s="1">
         <f>SUM(I3:I74)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="1">
         <f>SUM(K3:K74)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="1">
         <f>SUM(M3:M74)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="O1" s="1">
         <f>SUM(O3:O74)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="Q1" s="1">
         <f>SUM(Q3:Q74)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="S1" s="1">
         <f>SUM(S3:S74)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="U1" s="1">
         <f>SUM(U3:U74)</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="V1" s="2" t="s">
         <v>14</v>
       </c>
       <c r="W1" s="1">
         <f>SUM(W3:W74)</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="X1" s="2" t="s">
         <v>15</v>
       </c>
       <c r="Y1" s="1">
         <f>SUM(Y3:Y74)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="AA1" s="1">
         <f>SUM(AA3:AA74)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AB1" s="2" t="s">
         <v>17</v>
       </c>
       <c r="AC1" s="1">
         <f>SUM(AC3:AC74)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AD1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="AE1" s="1">
         <f>SUM(AE3:AE74)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF1" s="2" t="s">
         <v>19</v>
       </c>
       <c r="AG1" s="1">
         <f>SUM(AG3:AG74)</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH1" s="2" t="s">
         <v>20</v>
       </c>
       <c r="AI1" s="1">
         <f>SUM(AI3:AI74)</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ1" s="2" t="s">
         <v>21</v>
       </c>
       <c r="AK1" s="1">
         <f>SUM(AK3:AK74)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL1" s="2" t="s">
         <v>22</v>
       </c>
       <c r="AM1" s="1">
         <f>SUM(AM3:AM74)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AN1" s="2" t="s">
         <v>23</v>
       </c>
       <c r="AO1" s="1">
         <f>SUM(AO3:AO74)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AP1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="AQ1" s="1">
         <f>SUM(AQ3:AQ74)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AR1" s="2" t="s">
         <v>25</v>
       </c>
       <c r="AS1" s="1">
         <f>SUM(AS3:AS74)</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AT1" s="2" t="s">
         <v>26</v>
       </c>
       <c r="AU1" s="1">
         <f>SUM(AU3:AU74)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AV1" s="2" t="s">
         <v>27</v>
       </c>
       <c r="AW1" s="1">
         <f>SUM(AW3:AW74)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" ht="21.75" customHeight="1">
@@ -1172,155 +1172,153 @@
       <c r="F3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="5">
-        <v>2.0</v>
-      </c>
+      <c r="G3" s="5"/>
       <c r="H3" s="6">
         <v>1.0</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="7" t="str">
         <f t="shared" ref="I3:I74" si="1">IF($G3&lt;&gt;"",IF(H3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J3" s="6">
         <v>1.0</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="7" t="str">
         <f t="shared" ref="K3:K74" si="2">IF($G3&lt;&gt;"",IF(J3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L3" s="6">
         <v>1.0</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="7" t="str">
         <f t="shared" ref="M3:M74" si="3">IF($G3&lt;&gt;"",IF(L3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="O3" s="7">
+      <c r="O3" s="7" t="str">
         <f t="shared" ref="O3:O74" si="4">IF($G3&lt;&gt;"",IF(N3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P3" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q3" s="7">
+      <c r="Q3" s="7" t="str">
         <f t="shared" ref="Q3:Q74" si="5">IF($G3&lt;&gt;"",IF(P3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R3" s="6">
         <v>1.0</v>
       </c>
-      <c r="S3" s="7">
+      <c r="S3" s="7" t="str">
         <f t="shared" ref="S3:S74" si="6">IF($G3&lt;&gt;"",IF(R3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T3" s="6">
         <v>1.0</v>
       </c>
-      <c r="U3" s="7">
+      <c r="U3" s="7" t="str">
         <f t="shared" ref="U3:U74" si="7">IF($G3&lt;&gt;"",IF(T3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="V3" s="6">
         <v>1.0</v>
       </c>
-      <c r="W3" s="7">
+      <c r="W3" s="7" t="str">
         <f t="shared" ref="W3:W74" si="8">IF($G3&lt;&gt;"",IF(V3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="X3" s="6">
         <v>1.0</v>
       </c>
-      <c r="Y3" s="7">
+      <c r="Y3" s="7" t="str">
         <f t="shared" ref="Y3:Y74" si="9">IF($G3&lt;&gt;"",IF(X3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Z3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AA3" s="7">
+      <c r="AA3" s="7" t="str">
         <f t="shared" ref="AA3:AA74" si="10">IF($G3&lt;&gt;"",IF(Z3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AB3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AC3" s="7">
+      <c r="AC3" s="7" t="str">
         <f t="shared" ref="AC3:AC74" si="11">IF($G3&lt;&gt;"",IF(AB3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AD3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AE3" s="7">
+      <c r="AE3" s="7" t="str">
         <f t="shared" ref="AE3:AE74" si="12">IF($G3&lt;&gt;"",IF(AD3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AF3" s="6">
         <v>2.0</v>
       </c>
-      <c r="AG3" s="7">
+      <c r="AG3" s="7" t="str">
         <f t="shared" ref="AG3:AG74" si="13">IF($G3&lt;&gt;"",IF(AF3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AH3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AI3" s="7">
+      <c r="AI3" s="7" t="str">
         <f t="shared" ref="AI3:AI74" si="14">IF($G3&lt;&gt;"",IF(AH3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AJ3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AK3" s="7">
+      <c r="AK3" s="7" t="str">
         <f t="shared" ref="AK3:AK74" si="15">IF($G3&lt;&gt;"",IF(AJ3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AM3" s="7">
+      <c r="AM3" s="7" t="str">
         <f t="shared" ref="AM3:AM74" si="16">IF($G3&lt;&gt;"",IF(AL3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AN3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO3" s="7">
+      <c r="AO3" s="7" t="str">
         <f t="shared" ref="AO3:AO74" si="17">IF($G3&lt;&gt;"",IF(AN3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AP3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AQ3" s="7">
+      <c r="AQ3" s="7" t="str">
         <f t="shared" ref="AQ3:AQ74" si="18">IF($G3&lt;&gt;"",IF(AP3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AS3" s="7">
+      <c r="AS3" s="7" t="str">
         <f t="shared" ref="AS3:AS74" si="19">IF($G3&lt;&gt;"",IF(AR3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AU3" s="7">
+      <c r="AU3" s="7" t="str">
         <f t="shared" ref="AU3:AU74" si="20">IF($G3&lt;&gt;"",IF(AT3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AV3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AW3" s="7">
+      <c r="AW3" s="7" t="str">
         <f t="shared" ref="AW3:AW74" si="21">IF($G3&lt;&gt;"",IF(AV3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="4" ht="18.0" customHeight="1">
@@ -1342,155 +1340,153 @@
       <c r="F4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>36</v>
-      </c>
+      <c r="G4" s="5"/>
       <c r="H4" s="6">
         <v>1.0</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J4" s="6">
         <v>2.0</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L4" s="6">
         <v>2.0</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N4" s="6">
         <v>2.0</v>
       </c>
-      <c r="O4" s="7">
+      <c r="O4" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="Q4" s="7">
+      <c r="Q4" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="R4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="S4" s="7">
+      <c r="S4" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="T4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="U4" s="7">
+      <c r="U4" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="V4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="W4" s="7">
+      <c r="W4" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="X4" s="6">
         <v>1.0</v>
       </c>
-      <c r="Y4" s="7">
+      <c r="Y4" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Z4" s="6">
         <v>2.0</v>
       </c>
-      <c r="AA4" s="7">
+      <c r="AA4" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AB4" s="6">
         <v>1.0</v>
       </c>
-      <c r="AC4" s="7">
+      <c r="AC4" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AD4" s="6">
         <v>2.0</v>
       </c>
-      <c r="AE4" s="7">
+      <c r="AE4" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AF4" s="6">
         <v>1.0</v>
       </c>
-      <c r="AG4" s="7">
+      <c r="AG4" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AH4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AI4" s="7">
+      <c r="AI4" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AJ4" s="6">
         <v>1.0</v>
       </c>
-      <c r="AK4" s="7">
+      <c r="AK4" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL4" s="6">
         <v>1.0</v>
       </c>
-      <c r="AM4" s="7">
+      <c r="AM4" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AN4" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO4" s="7">
+      <c r="AO4" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AP4" s="6">
         <v>1.0</v>
       </c>
-      <c r="AQ4" s="7">
+      <c r="AQ4" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR4" s="6">
         <v>2.0</v>
       </c>
-      <c r="AS4" s="7">
+      <c r="AS4" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AU4" s="7">
+      <c r="AU4" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AV4" s="6">
         <v>2.0</v>
       </c>
-      <c r="AW4" s="7">
+      <c r="AW4" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="5" ht="18.0" customHeight="1">
@@ -1512,155 +1508,153 @@
       <c r="F5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="5">
-        <v>2.0</v>
-      </c>
+      <c r="G5" s="5"/>
       <c r="H5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N5" s="6">
         <v>2.0</v>
       </c>
-      <c r="O5" s="7">
+      <c r="O5" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="P5" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q5" s="7">
+      <c r="Q5" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R5" s="6">
         <v>2.0</v>
       </c>
-      <c r="S5" s="7">
+      <c r="S5" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="T5" s="6">
         <v>1.0</v>
       </c>
-      <c r="U5" s="7">
+      <c r="U5" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="V5" s="6">
         <v>1.0</v>
       </c>
-      <c r="W5" s="7">
+      <c r="W5" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="X5" s="6">
         <v>1.0</v>
       </c>
-      <c r="Y5" s="7">
+      <c r="Y5" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Z5" s="6">
         <v>1.0</v>
       </c>
-      <c r="AA5" s="7">
+      <c r="AA5" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AB5" s="6">
         <v>1.0</v>
       </c>
-      <c r="AC5" s="7">
+      <c r="AC5" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AD5" s="6">
         <v>1.0</v>
       </c>
-      <c r="AE5" s="7">
+      <c r="AE5" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AF5" s="6">
         <v>2.0</v>
       </c>
-      <c r="AG5" s="7">
+      <c r="AG5" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AH5" s="6">
         <v>1.0</v>
       </c>
-      <c r="AI5" s="7">
+      <c r="AI5" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AJ5" s="6">
         <v>1.0</v>
       </c>
-      <c r="AK5" s="7">
+      <c r="AK5" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL5" s="6">
         <v>2.0</v>
       </c>
-      <c r="AM5" s="7">
+      <c r="AM5" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AN5" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO5" s="7">
+      <c r="AO5" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AP5" s="6">
         <v>1.0</v>
       </c>
-      <c r="AQ5" s="7">
+      <c r="AQ5" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR5" s="6">
         <v>1.0</v>
       </c>
-      <c r="AS5" s="7">
+      <c r="AS5" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT5" s="6">
         <v>2.0</v>
       </c>
-      <c r="AU5" s="7">
+      <c r="AU5" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AV5" s="6">
         <v>2.0</v>
       </c>
-      <c r="AW5" s="7">
+      <c r="AW5" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="6" ht="18.0" customHeight="1">
@@ -1682,155 +1676,153 @@
       <c r="F6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="5">
-        <v>2.0</v>
-      </c>
+      <c r="G6" s="5"/>
       <c r="H6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J6" s="6">
         <v>1.0</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L6" s="6">
         <v>1.0</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N6" s="6">
         <v>1.0</v>
       </c>
-      <c r="O6" s="7">
+      <c r="O6" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="Q6" s="7">
+      <c r="Q6" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R6" s="6">
         <v>1.0</v>
       </c>
-      <c r="S6" s="7">
+      <c r="S6" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="U6" s="7">
+      <c r="U6" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="V6" s="6">
         <v>1.0</v>
       </c>
-      <c r="W6" s="7">
+      <c r="W6" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="X6" s="6">
         <v>1.0</v>
       </c>
-      <c r="Y6" s="7">
+      <c r="Y6" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Z6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AA6" s="7">
+      <c r="AA6" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AB6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AC6" s="7">
+      <c r="AC6" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AD6" s="6">
         <v>1.0</v>
       </c>
-      <c r="AE6" s="7">
+      <c r="AE6" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AF6" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AG6" s="7">
+      <c r="AG6" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AH6" s="6">
         <v>1.0</v>
       </c>
-      <c r="AI6" s="7">
+      <c r="AI6" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AJ6" s="6">
         <v>1.0</v>
       </c>
-      <c r="AK6" s="7">
+      <c r="AK6" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AM6" s="7">
+      <c r="AM6" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AN6" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO6" s="7">
+      <c r="AO6" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AP6" s="6">
         <v>1.0</v>
       </c>
-      <c r="AQ6" s="7">
+      <c r="AQ6" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR6" s="6">
         <v>1.0</v>
       </c>
-      <c r="AS6" s="7">
+      <c r="AS6" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT6" s="6">
         <v>2.0</v>
       </c>
-      <c r="AU6" s="7">
+      <c r="AU6" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AV6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AW6" s="7">
+      <c r="AW6" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="7" ht="18.0" customHeight="1">
@@ -1852,155 +1844,153 @@
       <c r="F7" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="5">
-        <v>2.0</v>
-      </c>
+      <c r="G7" s="5"/>
       <c r="H7" s="6">
         <v>2.0</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J7" s="6">
         <v>2.0</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="L7" s="6">
         <v>1.0</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N7" s="6">
         <v>2.0</v>
       </c>
-      <c r="O7" s="7">
+      <c r="O7" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="P7" s="6">
         <v>2.0</v>
       </c>
-      <c r="Q7" s="7">
+      <c r="Q7" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="R7" s="6">
         <v>2.0</v>
       </c>
-      <c r="S7" s="7">
+      <c r="S7" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="T7" s="6">
         <v>2.0</v>
       </c>
-      <c r="U7" s="7">
+      <c r="U7" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="V7" s="6">
         <v>2.0</v>
       </c>
-      <c r="W7" s="7">
+      <c r="W7" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="X7" s="6">
         <v>2.0</v>
       </c>
-      <c r="Y7" s="7">
+      <c r="Y7" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Z7" s="6">
         <v>1.0</v>
       </c>
-      <c r="AA7" s="7">
+      <c r="AA7" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AB7" s="6">
         <v>2.0</v>
       </c>
-      <c r="AC7" s="7">
+      <c r="AC7" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AD7" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AE7" s="7">
+      <c r="AE7" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AF7" s="6">
         <v>2.0</v>
       </c>
-      <c r="AG7" s="7">
+      <c r="AG7" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AH7" s="6">
         <v>2.0</v>
       </c>
-      <c r="AI7" s="7">
+      <c r="AI7" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AJ7" s="6">
         <v>2.0</v>
       </c>
-      <c r="AK7" s="7">
+      <c r="AK7" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AL7" s="6">
         <v>2.0</v>
       </c>
-      <c r="AM7" s="7">
+      <c r="AM7" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AN7" s="6">
         <v>2.0</v>
       </c>
-      <c r="AO7" s="7">
+      <c r="AO7" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AP7" s="6">
         <v>2.0</v>
       </c>
-      <c r="AQ7" s="7">
+      <c r="AQ7" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AR7" s="6">
         <v>2.0</v>
       </c>
-      <c r="AS7" s="7">
+      <c r="AS7" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AT7" s="6">
         <v>2.0</v>
       </c>
-      <c r="AU7" s="7">
+      <c r="AU7" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AV7" s="6">
         <v>2.0</v>
       </c>
-      <c r="AW7" s="7">
+      <c r="AW7" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="8" ht="18.0" customHeight="1">
@@ -2022,155 +2012,153 @@
       <c r="F8" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="G8" s="5">
-        <v>2.0</v>
-      </c>
+      <c r="G8" s="5"/>
       <c r="H8" s="6">
         <v>1.0</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J8" s="6">
         <v>1.0</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L8" s="6">
         <v>1.0</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="O8" s="7">
+      <c r="O8" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="Q8" s="7">
+      <c r="Q8" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="S8" s="7">
+      <c r="S8" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T8" s="6">
         <v>1.0</v>
       </c>
-      <c r="U8" s="7">
+      <c r="U8" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="V8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="W8" s="7">
+      <c r="W8" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="X8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="Y8" s="7">
+      <c r="Y8" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Z8" s="6">
         <v>1.0</v>
       </c>
-      <c r="AA8" s="7">
+      <c r="AA8" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AB8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AC8" s="7">
+      <c r="AC8" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AD8" s="6">
         <v>1.0</v>
       </c>
-      <c r="AE8" s="7">
+      <c r="AE8" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AF8" s="6">
         <v>1.0</v>
       </c>
-      <c r="AG8" s="7">
+      <c r="AG8" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AH8" s="6">
         <v>1.0</v>
       </c>
-      <c r="AI8" s="7">
+      <c r="AI8" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AJ8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AK8" s="7">
+      <c r="AK8" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AM8" s="7">
+      <c r="AM8" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AN8" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO8" s="7">
+      <c r="AO8" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AP8" s="6">
         <v>1.0</v>
       </c>
-      <c r="AQ8" s="7">
+      <c r="AQ8" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR8" s="6">
         <v>1.0</v>
       </c>
-      <c r="AS8" s="7">
+      <c r="AS8" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT8" s="6">
         <v>1.0</v>
       </c>
-      <c r="AU8" s="7">
+      <c r="AU8" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AV8" s="6">
         <v>1.0</v>
       </c>
-      <c r="AW8" s="7">
+      <c r="AW8" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="9" ht="18.0" customHeight="1">
@@ -2192,155 +2180,153 @@
       <c r="F9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="5">
-        <v>2.0</v>
-      </c>
+      <c r="G9" s="5"/>
       <c r="H9" s="6">
         <v>2.0</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J9" s="6">
         <v>2.0</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="L9" s="6">
         <v>2.0</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="N9" s="6">
         <v>2.0</v>
       </c>
-      <c r="O9" s="7">
+      <c r="O9" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="P9" s="6">
         <v>2.0</v>
       </c>
-      <c r="Q9" s="7">
+      <c r="Q9" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="R9" s="6">
         <v>2.0</v>
       </c>
-      <c r="S9" s="7">
+      <c r="S9" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="T9" s="6">
         <v>2.0</v>
       </c>
-      <c r="U9" s="7">
+      <c r="U9" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="V9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="W9" s="7">
+      <c r="W9" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="X9" s="6">
         <v>2.0</v>
       </c>
-      <c r="Y9" s="7">
+      <c r="Y9" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Z9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AA9" s="7">
+      <c r="AA9" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AB9" s="6">
         <v>2.0</v>
       </c>
-      <c r="AC9" s="7">
+      <c r="AC9" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AD9" s="6">
         <v>2.0</v>
       </c>
-      <c r="AE9" s="7">
+      <c r="AE9" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AF9" s="6">
         <v>2.0</v>
       </c>
-      <c r="AG9" s="7">
+      <c r="AG9" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AH9" s="6">
         <v>2.0</v>
       </c>
-      <c r="AI9" s="7">
+      <c r="AI9" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AJ9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AK9" s="7">
+      <c r="AK9" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AM9" s="7">
+      <c r="AM9" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AN9" s="6">
         <v>2.0</v>
       </c>
-      <c r="AO9" s="7">
+      <c r="AO9" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AP9" s="6">
         <v>2.0</v>
       </c>
-      <c r="AQ9" s="7">
+      <c r="AQ9" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AR9" s="6">
         <v>2.0</v>
       </c>
-      <c r="AS9" s="7">
+      <c r="AS9" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AT9" s="6">
         <v>2.0</v>
       </c>
-      <c r="AU9" s="7">
+      <c r="AU9" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AV9" s="6">
         <v>2.0</v>
       </c>
-      <c r="AW9" s="7">
+      <c r="AW9" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="10" ht="18.0" customHeight="1">
@@ -2362,155 +2348,153 @@
       <c r="F10" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="5">
-        <v>1.0</v>
-      </c>
+      <c r="G10" s="5"/>
       <c r="H10" s="6">
         <v>2.0</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J10" s="6">
         <v>2.0</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L10" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M10" s="7">
+      <c r="M10" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N10" s="6">
         <v>2.0</v>
       </c>
-      <c r="O10" s="7">
+      <c r="O10" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P10" s="6">
         <v>2.0</v>
       </c>
-      <c r="Q10" s="7">
+      <c r="Q10" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R10" s="6">
         <v>2.0</v>
       </c>
-      <c r="S10" s="7">
+      <c r="S10" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T10" s="6">
         <v>2.0</v>
       </c>
-      <c r="U10" s="7">
+      <c r="U10" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="V10" s="6">
         <v>2.0</v>
       </c>
-      <c r="W10" s="7">
+      <c r="W10" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="X10" s="6">
         <v>2.0</v>
       </c>
-      <c r="Y10" s="7">
+      <c r="Y10" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Z10" s="6">
         <v>2.0</v>
       </c>
-      <c r="AA10" s="7">
+      <c r="AA10" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AB10" s="6">
         <v>2.0</v>
       </c>
-      <c r="AC10" s="7">
+      <c r="AC10" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AD10" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AE10" s="7">
+      <c r="AE10" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AF10" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AG10" s="7">
+      <c r="AG10" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AH10" s="6">
         <v>2.0</v>
       </c>
-      <c r="AI10" s="7">
+      <c r="AI10" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AJ10" s="6">
         <v>1.0</v>
       </c>
-      <c r="AK10" s="7">
+      <c r="AK10" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AL10" s="6">
         <v>1.0</v>
       </c>
-      <c r="AM10" s="7">
+      <c r="AM10" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AN10" s="6">
         <v>2.0</v>
       </c>
-      <c r="AO10" s="7">
+      <c r="AO10" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AP10" s="6">
         <v>2.0</v>
       </c>
-      <c r="AQ10" s="7">
+      <c r="AQ10" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR10" s="6">
         <v>1.0</v>
       </c>
-      <c r="AS10" s="7">
+      <c r="AS10" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AT10" s="6">
         <v>2.0</v>
       </c>
-      <c r="AU10" s="7">
+      <c r="AU10" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AV10" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AW10" s="7">
+      <c r="AW10" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="11" ht="18.0" customHeight="1">
@@ -2532,155 +2516,153 @@
       <c r="F11" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>36</v>
-      </c>
+      <c r="G11" s="5"/>
       <c r="H11" s="6">
         <v>1.0</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J11" s="6">
         <v>1.0</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L11" s="6">
         <v>1.0</v>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N11" s="6">
         <v>1.0</v>
       </c>
-      <c r="O11" s="7">
+      <c r="O11" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P11" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q11" s="7">
+      <c r="Q11" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R11" s="6">
         <v>1.0</v>
       </c>
-      <c r="S11" s="7">
+      <c r="S11" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T11" s="6">
         <v>1.0</v>
       </c>
-      <c r="U11" s="7">
+      <c r="U11" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="V11" s="6">
         <v>1.0</v>
       </c>
-      <c r="W11" s="7">
+      <c r="W11" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="X11" s="6">
         <v>1.0</v>
       </c>
-      <c r="Y11" s="7">
+      <c r="Y11" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Z11" s="6">
         <v>1.0</v>
       </c>
-      <c r="AA11" s="7">
+      <c r="AA11" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AB11" s="6">
         <v>1.0</v>
       </c>
-      <c r="AC11" s="7">
+      <c r="AC11" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AD11" s="6">
         <v>1.0</v>
       </c>
-      <c r="AE11" s="7">
+      <c r="AE11" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AF11" s="6">
         <v>1.0</v>
       </c>
-      <c r="AG11" s="7">
+      <c r="AG11" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AH11" s="6">
         <v>1.0</v>
       </c>
-      <c r="AI11" s="7">
+      <c r="AI11" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AJ11" s="6">
         <v>1.0</v>
       </c>
-      <c r="AK11" s="7">
+      <c r="AK11" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL11" s="6">
         <v>1.0</v>
       </c>
-      <c r="AM11" s="7">
+      <c r="AM11" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AN11" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO11" s="7">
+      <c r="AO11" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AP11" s="6">
         <v>1.0</v>
       </c>
-      <c r="AQ11" s="7">
+      <c r="AQ11" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR11" s="6">
         <v>1.0</v>
       </c>
-      <c r="AS11" s="7">
+      <c r="AS11" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT11" s="6">
         <v>1.0</v>
       </c>
-      <c r="AU11" s="7">
+      <c r="AU11" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AV11" s="6">
         <v>1.0</v>
       </c>
-      <c r="AW11" s="7">
+      <c r="AW11" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="12" ht="18.0" customHeight="1">
@@ -2702,155 +2684,153 @@
       <c r="F12" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G12" s="5">
-        <v>1.0</v>
-      </c>
+      <c r="G12" s="5"/>
       <c r="H12" s="6">
         <v>1.0</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J12" s="6">
         <v>1.0</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="L12" s="6">
         <v>1.0</v>
       </c>
-      <c r="M12" s="7">
+      <c r="M12" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="N12" s="6">
         <v>2.0</v>
       </c>
-      <c r="O12" s="7">
+      <c r="O12" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P12" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="Q12" s="7">
+      <c r="Q12" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R12" s="6">
         <v>1.0</v>
       </c>
-      <c r="S12" s="7">
+      <c r="S12" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="T12" s="6">
         <v>1.0</v>
       </c>
-      <c r="U12" s="7">
+      <c r="U12" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="V12" s="6">
         <v>1.0</v>
       </c>
-      <c r="W12" s="7">
+      <c r="W12" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="X12" s="6">
         <v>1.0</v>
       </c>
-      <c r="Y12" s="7">
+      <c r="Y12" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Z12" s="6">
         <v>1.0</v>
       </c>
-      <c r="AA12" s="7">
+      <c r="AA12" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AB12" s="6">
         <v>2.0</v>
       </c>
-      <c r="AC12" s="7">
+      <c r="AC12" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AD12" s="6">
         <v>1.0</v>
       </c>
-      <c r="AE12" s="7">
+      <c r="AE12" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AF12" s="6">
         <v>1.0</v>
       </c>
-      <c r="AG12" s="7">
+      <c r="AG12" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AH12" s="6">
         <v>1.0</v>
       </c>
-      <c r="AI12" s="7">
+      <c r="AI12" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AJ12" s="6">
         <v>1.0</v>
       </c>
-      <c r="AK12" s="7">
+      <c r="AK12" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AL12" s="6">
         <v>1.0</v>
       </c>
-      <c r="AM12" s="7">
+      <c r="AM12" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AN12" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO12" s="7">
+      <c r="AO12" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AP12" s="6">
         <v>1.0</v>
       </c>
-      <c r="AQ12" s="7">
+      <c r="AQ12" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AR12" s="6">
         <v>1.0</v>
       </c>
-      <c r="AS12" s="7">
+      <c r="AS12" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AT12" s="6">
         <v>1.0</v>
       </c>
-      <c r="AU12" s="7">
+      <c r="AU12" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AV12" s="6">
         <v>1.0</v>
       </c>
-      <c r="AW12" s="7">
+      <c r="AW12" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="13" ht="18.0" customHeight="1">
@@ -2872,155 +2852,153 @@
       <c r="F13" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="G13" s="5">
-        <v>1.0</v>
-      </c>
+      <c r="G13" s="5"/>
       <c r="H13" s="6">
         <v>1.0</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="K13" s="7">
+      <c r="K13" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M13" s="7">
+      <c r="M13" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N13" s="6">
         <v>1.0</v>
       </c>
-      <c r="O13" s="7">
+      <c r="O13" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="P13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="Q13" s="7">
+      <c r="Q13" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="S13" s="7">
+      <c r="S13" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T13" s="6">
         <v>2.0</v>
       </c>
-      <c r="U13" s="7">
+      <c r="U13" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="V13" s="6">
         <v>1.0</v>
       </c>
-      <c r="W13" s="7">
+      <c r="W13" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="X13" s="6">
         <v>2.0</v>
       </c>
-      <c r="Y13" s="7">
+      <c r="Y13" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Z13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AA13" s="7">
+      <c r="AA13" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AB13" s="6">
         <v>1.0</v>
       </c>
-      <c r="AC13" s="7">
+      <c r="AC13" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AD13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AE13" s="7">
+      <c r="AE13" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AF13" s="6">
         <v>1.0</v>
       </c>
-      <c r="AG13" s="7">
+      <c r="AG13" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AH13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AI13" s="7">
+      <c r="AI13" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AJ13" s="6">
         <v>1.0</v>
       </c>
-      <c r="AK13" s="7">
+      <c r="AK13" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AL13" s="6">
         <v>2.0</v>
       </c>
-      <c r="AM13" s="7">
+      <c r="AM13" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AN13" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO13" s="7">
+      <c r="AO13" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AP13" s="6">
         <v>2.0</v>
       </c>
-      <c r="AQ13" s="7">
+      <c r="AQ13" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR13" s="6">
         <v>1.0</v>
       </c>
-      <c r="AS13" s="7">
+      <c r="AS13" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AT13" s="6">
         <v>2.0</v>
       </c>
-      <c r="AU13" s="7">
+      <c r="AU13" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AV13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AW13" s="7">
+      <c r="AW13" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="14" ht="18.0" customHeight="1">
@@ -3042,155 +3020,153 @@
       <c r="F14" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="5">
-        <v>1.0</v>
-      </c>
+      <c r="G14" s="5"/>
       <c r="H14" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J14" s="6">
         <v>1.0</v>
       </c>
-      <c r="K14" s="7">
+      <c r="K14" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="L14" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M14" s="7">
+      <c r="M14" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N14" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="O14" s="7">
+      <c r="O14" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P14" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q14" s="7">
+      <c r="Q14" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="R14" s="6">
         <v>1.0</v>
       </c>
-      <c r="S14" s="7">
+      <c r="S14" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="T14" s="6">
         <v>1.0</v>
       </c>
-      <c r="U14" s="7">
+      <c r="U14" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="V14" s="6">
         <v>1.0</v>
       </c>
-      <c r="W14" s="7">
+      <c r="W14" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="X14" s="6">
         <v>1.0</v>
       </c>
-      <c r="Y14" s="7">
+      <c r="Y14" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Z14" s="6">
         <v>1.0</v>
       </c>
-      <c r="AA14" s="7">
+      <c r="AA14" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AB14" s="6">
         <v>1.0</v>
       </c>
-      <c r="AC14" s="7">
+      <c r="AC14" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AD14" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AE14" s="7">
+      <c r="AE14" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AF14" s="6">
         <v>1.0</v>
       </c>
-      <c r="AG14" s="7">
+      <c r="AG14" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AH14" s="6">
         <v>1.0</v>
       </c>
-      <c r="AI14" s="7">
+      <c r="AI14" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AJ14" s="6">
         <v>2.0</v>
       </c>
-      <c r="AK14" s="7">
+      <c r="AK14" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL14" s="6">
         <v>1.0</v>
       </c>
-      <c r="AM14" s="7">
+      <c r="AM14" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AN14" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO14" s="7">
+      <c r="AO14" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AP14" s="6">
         <v>2.0</v>
       </c>
-      <c r="AQ14" s="7">
+      <c r="AQ14" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR14" s="6">
         <v>1.0</v>
       </c>
-      <c r="AS14" s="7">
+      <c r="AS14" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AT14" s="6">
         <v>1.0</v>
       </c>
-      <c r="AU14" s="7">
+      <c r="AU14" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AV14" s="6">
         <v>2.0</v>
       </c>
-      <c r="AW14" s="7">
+      <c r="AW14" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="15" ht="18.0" customHeight="1">
@@ -3212,155 +3188,153 @@
       <c r="F15" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="5">
-        <v>1.0</v>
-      </c>
+      <c r="G15" s="5"/>
       <c r="H15" s="6">
         <v>1.0</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J15" s="6">
         <v>1.0</v>
       </c>
-      <c r="K15" s="7">
+      <c r="K15" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="L15" s="6">
         <v>1.0</v>
       </c>
-      <c r="M15" s="7">
+      <c r="M15" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="N15" s="6">
         <v>1.0</v>
       </c>
-      <c r="O15" s="7">
+      <c r="O15" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="P15" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q15" s="7">
+      <c r="Q15" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="R15" s="6">
         <v>1.0</v>
       </c>
-      <c r="S15" s="7">
+      <c r="S15" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="T15" s="6">
         <v>1.0</v>
       </c>
-      <c r="U15" s="7">
+      <c r="U15" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="V15" s="6">
         <v>1.0</v>
       </c>
-      <c r="W15" s="7">
+      <c r="W15" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="X15" s="6">
         <v>1.0</v>
       </c>
-      <c r="Y15" s="7">
+      <c r="Y15" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Z15" s="6">
         <v>1.0</v>
       </c>
-      <c r="AA15" s="7">
+      <c r="AA15" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AB15" s="6">
         <v>1.0</v>
       </c>
-      <c r="AC15" s="7">
+      <c r="AC15" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AD15" s="6">
         <v>1.0</v>
       </c>
-      <c r="AE15" s="7">
+      <c r="AE15" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AF15" s="6">
         <v>1.0</v>
       </c>
-      <c r="AG15" s="7">
+      <c r="AG15" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AH15" s="6">
         <v>1.0</v>
       </c>
-      <c r="AI15" s="7">
+      <c r="AI15" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AJ15" s="6">
         <v>1.0</v>
       </c>
-      <c r="AK15" s="7">
+      <c r="AK15" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AL15" s="6">
         <v>1.0</v>
       </c>
-      <c r="AM15" s="7">
+      <c r="AM15" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AN15" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO15" s="7">
+      <c r="AO15" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AP15" s="6">
         <v>1.0</v>
       </c>
-      <c r="AQ15" s="7">
+      <c r="AQ15" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AR15" s="6">
         <v>1.0</v>
       </c>
-      <c r="AS15" s="7">
+      <c r="AS15" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AT15" s="6">
         <v>1.0</v>
       </c>
-      <c r="AU15" s="7">
+      <c r="AU15" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AV15" s="6">
         <v>1.0</v>
       </c>
-      <c r="AW15" s="7">
+      <c r="AW15" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="16" ht="18.0" customHeight="1">
@@ -3382,155 +3356,153 @@
       <c r="F16" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G16" s="5">
-        <v>1.0</v>
-      </c>
+      <c r="G16" s="5"/>
       <c r="H16" s="6">
         <v>1.0</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J16" s="6">
         <v>1.0</v>
       </c>
-      <c r="K16" s="7">
+      <c r="K16" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="L16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M16" s="7">
+      <c r="M16" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N16" s="6">
         <v>2.0</v>
       </c>
-      <c r="O16" s="7">
+      <c r="O16" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P16" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q16" s="7">
+      <c r="Q16" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="R16" s="6">
         <v>1.0</v>
       </c>
-      <c r="S16" s="7">
+      <c r="S16" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="T16" s="6">
         <v>1.0</v>
       </c>
-      <c r="U16" s="7">
+      <c r="U16" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="V16" s="6">
         <v>1.0</v>
       </c>
-      <c r="W16" s="7">
+      <c r="W16" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="X16" s="6">
         <v>1.0</v>
       </c>
-      <c r="Y16" s="7">
+      <c r="Y16" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Z16" s="6">
         <v>1.0</v>
       </c>
-      <c r="AA16" s="7">
+      <c r="AA16" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AB16" s="6">
         <v>1.0</v>
       </c>
-      <c r="AC16" s="7">
+      <c r="AC16" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AD16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AE16" s="7">
+      <c r="AE16" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AF16" s="6">
         <v>1.0</v>
       </c>
-      <c r="AG16" s="7">
+      <c r="AG16" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AH16" s="6">
         <v>1.0</v>
       </c>
-      <c r="AI16" s="7">
+      <c r="AI16" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AJ16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AK16" s="7">
+      <c r="AK16" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AM16" s="7">
+      <c r="AM16" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AN16" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO16" s="7">
+      <c r="AO16" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AP16" s="6">
         <v>1.0</v>
       </c>
-      <c r="AQ16" s="7">
+      <c r="AQ16" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AR16" s="6">
         <v>1.0</v>
       </c>
-      <c r="AS16" s="7">
+      <c r="AS16" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AT16" s="6">
         <v>1.0</v>
       </c>
-      <c r="AU16" s="7">
+      <c r="AU16" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AV16" s="6">
         <v>1.0</v>
       </c>
-      <c r="AW16" s="7">
+      <c r="AW16" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="17" ht="18.0" customHeight="1">
@@ -3552,155 +3524,153 @@
       <c r="F17" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G17" s="5">
-        <v>1.0</v>
-      </c>
+      <c r="G17" s="5"/>
       <c r="H17" s="6">
         <v>2.0</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I17" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J17" s="6">
         <v>2.0</v>
       </c>
-      <c r="K17" s="7">
+      <c r="K17" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L17" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M17" s="7">
+      <c r="M17" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N17" s="6">
         <v>2.0</v>
       </c>
-      <c r="O17" s="7">
+      <c r="O17" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P17" s="6">
         <v>2.0</v>
       </c>
-      <c r="Q17" s="7">
+      <c r="Q17" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R17" s="6">
         <v>2.0</v>
       </c>
-      <c r="S17" s="7">
+      <c r="S17" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T17" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="U17" s="7">
+      <c r="U17" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="V17" s="6">
         <v>2.0</v>
       </c>
-      <c r="W17" s="7">
+      <c r="W17" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="X17" s="6">
         <v>2.0</v>
       </c>
-      <c r="Y17" s="7">
+      <c r="Y17" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Z17" s="6">
         <v>1.0</v>
       </c>
-      <c r="AA17" s="7">
+      <c r="AA17" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AB17" s="6">
         <v>2.0</v>
       </c>
-      <c r="AC17" s="7">
+      <c r="AC17" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AD17" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AE17" s="7">
+      <c r="AE17" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AF17" s="6">
         <v>2.0</v>
       </c>
-      <c r="AG17" s="7">
+      <c r="AG17" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AH17" s="6">
         <v>2.0</v>
       </c>
-      <c r="AI17" s="7">
+      <c r="AI17" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AJ17" s="6">
         <v>2.0</v>
       </c>
-      <c r="AK17" s="7">
+      <c r="AK17" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL17" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AM17" s="7">
+      <c r="AM17" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AN17" s="6">
         <v>2.0</v>
       </c>
-      <c r="AO17" s="7">
+      <c r="AO17" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AP17" s="6">
         <v>2.0</v>
       </c>
-      <c r="AQ17" s="7">
+      <c r="AQ17" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR17" s="6">
         <v>2.0</v>
       </c>
-      <c r="AS17" s="7">
+      <c r="AS17" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT17" s="6">
         <v>2.0</v>
       </c>
-      <c r="AU17" s="7">
+      <c r="AU17" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AV17" s="6">
         <v>2.0</v>
       </c>
-      <c r="AW17" s="7">
+      <c r="AW17" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="18" ht="18.0" customHeight="1">
@@ -3722,155 +3692,153 @@
       <c r="F18" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="G18" s="5">
-        <v>1.0</v>
-      </c>
+      <c r="G18" s="5"/>
       <c r="H18" s="6">
         <v>1.0</v>
       </c>
-      <c r="I18" s="7">
+      <c r="I18" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J18" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="K18" s="7">
+      <c r="K18" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L18" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M18" s="7">
+      <c r="M18" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N18" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="O18" s="7">
+      <c r="O18" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P18" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="Q18" s="7">
+      <c r="Q18" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R18" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="S18" s="7">
+      <c r="S18" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T18" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="U18" s="7">
+      <c r="U18" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="V18" s="6">
         <v>1.0</v>
       </c>
-      <c r="W18" s="7">
+      <c r="W18" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="X18" s="6">
         <v>1.0</v>
       </c>
-      <c r="Y18" s="7">
+      <c r="Y18" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Z18" s="6">
         <v>2.0</v>
       </c>
-      <c r="AA18" s="7">
+      <c r="AA18" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AB18" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AC18" s="7">
+      <c r="AC18" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AD18" s="6">
         <v>1.0</v>
       </c>
-      <c r="AE18" s="7">
+      <c r="AE18" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AF18" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AG18" s="7">
+      <c r="AG18" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AH18" s="6">
         <v>1.0</v>
       </c>
-      <c r="AI18" s="7">
+      <c r="AI18" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AJ18" s="6">
         <v>1.0</v>
       </c>
-      <c r="AK18" s="7">
+      <c r="AK18" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AL18" s="6">
         <v>1.0</v>
       </c>
-      <c r="AM18" s="7">
+      <c r="AM18" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AN18" s="6">
         <v>2.0</v>
       </c>
-      <c r="AO18" s="7">
+      <c r="AO18" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AP18" s="6">
         <v>1.0</v>
       </c>
-      <c r="AQ18" s="7">
+      <c r="AQ18" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AR18" s="6">
         <v>2.0</v>
       </c>
-      <c r="AS18" s="7">
+      <c r="AS18" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT18" s="6">
         <v>2.0</v>
       </c>
-      <c r="AU18" s="7">
+      <c r="AU18" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AV18" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AW18" s="7">
+      <c r="AW18" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="19" ht="18.0" customHeight="1">
@@ -3892,155 +3860,153 @@
       <c r="F19" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="G19" s="5">
-        <v>1.0</v>
-      </c>
+      <c r="G19" s="5"/>
       <c r="H19" s="6">
         <v>1.0</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I19" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J19" s="6">
         <v>1.0</v>
       </c>
-      <c r="K19" s="7">
+      <c r="K19" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="L19" s="6">
         <v>1.0</v>
       </c>
-      <c r="M19" s="7">
+      <c r="M19" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="N19" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="O19" s="7">
+      <c r="O19" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P19" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q19" s="7">
+      <c r="Q19" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="R19" s="6">
         <v>1.0</v>
       </c>
-      <c r="S19" s="7">
+      <c r="S19" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="T19" s="6">
         <v>1.0</v>
       </c>
-      <c r="U19" s="7">
+      <c r="U19" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="V19" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="W19" s="7">
+      <c r="W19" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="X19" s="6">
         <v>1.0</v>
       </c>
-      <c r="Y19" s="7">
+      <c r="Y19" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Z19" s="6">
         <v>1.0</v>
       </c>
-      <c r="AA19" s="7">
+      <c r="AA19" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AB19" s="6">
         <v>1.0</v>
       </c>
-      <c r="AC19" s="7">
+      <c r="AC19" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AD19" s="6">
         <v>1.0</v>
       </c>
-      <c r="AE19" s="7">
+      <c r="AE19" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AF19" s="6">
         <v>1.0</v>
       </c>
-      <c r="AG19" s="7">
+      <c r="AG19" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AH19" s="6">
         <v>1.0</v>
       </c>
-      <c r="AI19" s="7">
+      <c r="AI19" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AJ19" s="6">
         <v>2.0</v>
       </c>
-      <c r="AK19" s="7">
+      <c r="AK19" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL19" s="6">
         <v>1.0</v>
       </c>
-      <c r="AM19" s="7">
+      <c r="AM19" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AN19" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO19" s="7">
+      <c r="AO19" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AP19" s="6">
         <v>1.0</v>
       </c>
-      <c r="AQ19" s="7">
+      <c r="AQ19" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AR19" s="6">
         <v>1.0</v>
       </c>
-      <c r="AS19" s="7">
+      <c r="AS19" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AT19" s="6">
         <v>2.0</v>
       </c>
-      <c r="AU19" s="7">
+      <c r="AU19" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AV19" s="6">
         <v>1.0</v>
       </c>
-      <c r="AW19" s="7">
+      <c r="AW19" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="20" ht="18.0" customHeight="1">
@@ -4062,155 +4028,153 @@
       <c r="F20" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G20" s="5">
-        <v>1.0</v>
-      </c>
+      <c r="G20" s="5"/>
       <c r="H20" s="6">
         <v>2.0</v>
       </c>
-      <c r="I20" s="7">
+      <c r="I20" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J20" s="6">
         <v>2.0</v>
       </c>
-      <c r="K20" s="7">
+      <c r="K20" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L20" s="6">
         <v>2.0</v>
       </c>
-      <c r="M20" s="7">
+      <c r="M20" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N20" s="6">
         <v>2.0</v>
       </c>
-      <c r="O20" s="7">
+      <c r="O20" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P20" s="6">
         <v>2.0</v>
       </c>
-      <c r="Q20" s="7">
+      <c r="Q20" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R20" s="6">
         <v>2.0</v>
       </c>
-      <c r="S20" s="7">
+      <c r="S20" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T20" s="6">
         <v>2.0</v>
       </c>
-      <c r="U20" s="7">
+      <c r="U20" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="V20" s="6">
         <v>2.0</v>
       </c>
-      <c r="W20" s="7">
+      <c r="W20" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="X20" s="6">
         <v>2.0</v>
       </c>
-      <c r="Y20" s="7">
+      <c r="Y20" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Z20" s="6">
         <v>2.0</v>
       </c>
-      <c r="AA20" s="7">
+      <c r="AA20" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AB20" s="6">
         <v>2.0</v>
       </c>
-      <c r="AC20" s="7">
+      <c r="AC20" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AD20" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AE20" s="7">
+      <c r="AE20" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AF20" s="6">
         <v>2.0</v>
       </c>
-      <c r="AG20" s="7">
+      <c r="AG20" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AH20" s="6">
         <v>2.0</v>
       </c>
-      <c r="AI20" s="7">
+      <c r="AI20" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AJ20" s="6">
         <v>2.0</v>
       </c>
-      <c r="AK20" s="7">
+      <c r="AK20" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL20" s="6">
         <v>2.0</v>
       </c>
-      <c r="AM20" s="7">
+      <c r="AM20" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AN20" s="6">
         <v>2.0</v>
       </c>
-      <c r="AO20" s="7">
+      <c r="AO20" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AP20" s="6">
         <v>2.0</v>
       </c>
-      <c r="AQ20" s="7">
+      <c r="AQ20" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR20" s="6">
         <v>2.0</v>
       </c>
-      <c r="AS20" s="7">
+      <c r="AS20" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT20" s="6">
         <v>2.0</v>
       </c>
-      <c r="AU20" s="7">
+      <c r="AU20" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AV20" s="6">
         <v>2.0</v>
       </c>
-      <c r="AW20" s="7">
+      <c r="AW20" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="21" ht="18.0" customHeight="1">
@@ -4232,155 +4196,153 @@
       <c r="F21" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G21" s="5">
-        <v>1.0</v>
-      </c>
+      <c r="G21" s="5"/>
       <c r="H21" s="6">
         <v>1.0</v>
       </c>
-      <c r="I21" s="7">
+      <c r="I21" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J21" s="6">
         <v>1.0</v>
       </c>
-      <c r="K21" s="7">
+      <c r="K21" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="L21" s="6">
         <v>1.0</v>
       </c>
-      <c r="M21" s="7">
+      <c r="M21" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="N21" s="6">
         <v>1.0</v>
       </c>
-      <c r="O21" s="7">
+      <c r="O21" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="P21" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q21" s="7">
+      <c r="Q21" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="R21" s="6">
         <v>1.0</v>
       </c>
-      <c r="S21" s="7">
+      <c r="S21" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="T21" s="6">
         <v>1.0</v>
       </c>
-      <c r="U21" s="7">
+      <c r="U21" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="V21" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="W21" s="7">
+      <c r="W21" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="X21" s="6">
         <v>1.0</v>
       </c>
-      <c r="Y21" s="7">
+      <c r="Y21" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Z21" s="6">
         <v>1.0</v>
       </c>
-      <c r="AA21" s="7">
+      <c r="AA21" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AB21" s="6">
         <v>1.0</v>
       </c>
-      <c r="AC21" s="7">
+      <c r="AC21" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AD21" s="6">
         <v>1.0</v>
       </c>
-      <c r="AE21" s="7">
+      <c r="AE21" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AF21" s="6">
         <v>1.0</v>
       </c>
-      <c r="AG21" s="7">
+      <c r="AG21" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AH21" s="6">
         <v>1.0</v>
       </c>
-      <c r="AI21" s="7">
+      <c r="AI21" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AJ21" s="6">
         <v>1.0</v>
       </c>
-      <c r="AK21" s="7">
+      <c r="AK21" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AL21" s="6">
         <v>1.0</v>
       </c>
-      <c r="AM21" s="7">
+      <c r="AM21" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AN21" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO21" s="7">
+      <c r="AO21" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AP21" s="6">
         <v>1.0</v>
       </c>
-      <c r="AQ21" s="7">
+      <c r="AQ21" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AR21" s="6">
         <v>1.0</v>
       </c>
-      <c r="AS21" s="7">
+      <c r="AS21" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AT21" s="6">
         <v>1.0</v>
       </c>
-      <c r="AU21" s="7">
+      <c r="AU21" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AV21" s="6">
         <v>1.0</v>
       </c>
-      <c r="AW21" s="7">
+      <c r="AW21" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="22" ht="18.0" customHeight="1">
@@ -4402,155 +4364,153 @@
       <c r="F22" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="G22" s="5">
-        <v>1.0</v>
-      </c>
+      <c r="G22" s="5"/>
       <c r="H22" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I22" s="7">
+      <c r="I22" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J22" s="6">
         <v>1.0</v>
       </c>
-      <c r="K22" s="7">
+      <c r="K22" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="L22" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M22" s="7">
+      <c r="M22" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N22" s="6">
         <v>1.0</v>
       </c>
-      <c r="O22" s="7">
+      <c r="O22" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="P22" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q22" s="7">
+      <c r="Q22" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="R22" s="6">
         <v>1.0</v>
       </c>
-      <c r="S22" s="7">
+      <c r="S22" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="T22" s="6">
         <v>1.0</v>
       </c>
-      <c r="U22" s="7">
+      <c r="U22" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="V22" s="6">
         <v>1.0</v>
       </c>
-      <c r="W22" s="7">
+      <c r="W22" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="X22" s="6">
         <v>1.0</v>
       </c>
-      <c r="Y22" s="7">
+      <c r="Y22" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Z22" s="6">
         <v>1.0</v>
       </c>
-      <c r="AA22" s="7">
+      <c r="AA22" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AB22" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AC22" s="7">
+      <c r="AC22" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AD22" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AE22" s="7">
+      <c r="AE22" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AF22" s="6">
         <v>1.0</v>
       </c>
-      <c r="AG22" s="7">
+      <c r="AG22" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AH22" s="6">
         <v>1.0</v>
       </c>
-      <c r="AI22" s="7">
+      <c r="AI22" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AJ22" s="6">
         <v>1.0</v>
       </c>
-      <c r="AK22" s="7">
+      <c r="AK22" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AL22" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AM22" s="7">
+      <c r="AM22" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AN22" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO22" s="7">
+      <c r="AO22" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AP22" s="6">
         <v>1.0</v>
       </c>
-      <c r="AQ22" s="7">
+      <c r="AQ22" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AR22" s="6">
         <v>1.0</v>
       </c>
-      <c r="AS22" s="7">
+      <c r="AS22" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AT22" s="6">
         <v>1.0</v>
       </c>
-      <c r="AU22" s="7">
+      <c r="AU22" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AV22" s="6">
         <v>1.0</v>
       </c>
-      <c r="AW22" s="7">
+      <c r="AW22" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="23" ht="18.0" customHeight="1">
@@ -4572,155 +4532,153 @@
       <c r="F23" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>36</v>
-      </c>
+      <c r="G23" s="5"/>
       <c r="H23" s="6">
         <v>1.0</v>
       </c>
-      <c r="I23" s="7">
+      <c r="I23" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J23" s="6">
         <v>1.0</v>
       </c>
-      <c r="K23" s="7">
+      <c r="K23" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L23" s="6">
         <v>1.0</v>
       </c>
-      <c r="M23" s="7">
+      <c r="M23" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N23" s="6">
         <v>1.0</v>
       </c>
-      <c r="O23" s="7">
+      <c r="O23" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P23" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q23" s="7">
+      <c r="Q23" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R23" s="6">
         <v>1.0</v>
       </c>
-      <c r="S23" s="7">
+      <c r="S23" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T23" s="6">
         <v>1.0</v>
       </c>
-      <c r="U23" s="7">
+      <c r="U23" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="V23" s="6">
         <v>1.0</v>
       </c>
-      <c r="W23" s="7">
+      <c r="W23" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="X23" s="6">
         <v>1.0</v>
       </c>
-      <c r="Y23" s="7">
+      <c r="Y23" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Z23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AA23" s="7">
+      <c r="AA23" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AB23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AC23" s="7">
+      <c r="AC23" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AD23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AE23" s="7">
+      <c r="AE23" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AF23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AG23" s="7">
+      <c r="AG23" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AH23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AI23" s="7">
+      <c r="AI23" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AJ23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AK23" s="7">
+      <c r="AK23" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AM23" s="7">
+      <c r="AM23" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AN23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO23" s="7">
+      <c r="AO23" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AP23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AQ23" s="7">
+      <c r="AQ23" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AS23" s="7">
+      <c r="AS23" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AU23" s="7">
+      <c r="AU23" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AV23" s="6">
         <v>1.0</v>
       </c>
-      <c r="AW23" s="7">
+      <c r="AW23" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="24" ht="18.0" customHeight="1">
@@ -4742,155 +4700,153 @@
       <c r="F24" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>36</v>
-      </c>
+      <c r="G24" s="5"/>
       <c r="H24" s="6">
         <v>1.0</v>
       </c>
-      <c r="I24" s="7">
+      <c r="I24" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J24" s="6">
         <v>1.0</v>
       </c>
-      <c r="K24" s="7">
+      <c r="K24" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L24" s="6">
         <v>1.0</v>
       </c>
-      <c r="M24" s="7">
+      <c r="M24" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="O24" s="7">
+      <c r="O24" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="P24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="Q24" s="7">
+      <c r="Q24" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="R24" s="6">
         <v>1.0</v>
       </c>
-      <c r="S24" s="7">
+      <c r="S24" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T24" s="6">
         <v>1.0</v>
       </c>
-      <c r="U24" s="7">
+      <c r="U24" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="V24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="W24" s="7">
+      <c r="W24" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="X24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="Y24" s="7">
+      <c r="Y24" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Z24" s="6">
         <v>1.0</v>
       </c>
-      <c r="AA24" s="7">
+      <c r="AA24" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AB24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AC24" s="7">
+      <c r="AC24" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AD24" s="6">
         <v>1.0</v>
       </c>
-      <c r="AE24" s="7">
+      <c r="AE24" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AF24" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AG24" s="7">
+      <c r="AG24" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AH24" s="6">
         <v>1.0</v>
       </c>
-      <c r="AI24" s="7">
+      <c r="AI24" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AJ24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AK24" s="7">
+      <c r="AK24" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AL24" s="6">
         <v>2.0</v>
       </c>
-      <c r="AM24" s="7">
+      <c r="AM24" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AN24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AO24" s="7">
+      <c r="AO24" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AP24" s="6">
         <v>1.0</v>
       </c>
-      <c r="AQ24" s="7">
+      <c r="AQ24" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR24" s="6">
         <v>1.0</v>
       </c>
-      <c r="AS24" s="7">
+      <c r="AS24" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT24" s="6">
         <v>1.0</v>
       </c>
-      <c r="AU24" s="7">
+      <c r="AU24" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AV24" s="6">
         <v>1.0</v>
       </c>
-      <c r="AW24" s="7">
+      <c r="AW24" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="25" ht="18.0" customHeight="1">
@@ -4912,155 +4868,153 @@
       <c r="F25" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="G25" s="5">
-        <v>1.0</v>
-      </c>
+      <c r="G25" s="5"/>
       <c r="H25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I25" s="7">
+      <c r="I25" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J25" s="6">
         <v>1.0</v>
       </c>
-      <c r="K25" s="7">
+      <c r="K25" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="L25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M25" s="7">
+      <c r="M25" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N25" s="6">
         <v>1.0</v>
       </c>
-      <c r="O25" s="7">
+      <c r="O25" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="P25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="Q25" s="7">
+      <c r="Q25" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R25" s="6">
         <v>1.0</v>
       </c>
-      <c r="S25" s="7">
+      <c r="S25" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="T25" s="6">
         <v>1.0</v>
       </c>
-      <c r="U25" s="7">
+      <c r="U25" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="V25" s="6">
         <v>1.0</v>
       </c>
-      <c r="W25" s="7">
+      <c r="W25" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="X25" s="6">
         <v>1.0</v>
       </c>
-      <c r="Y25" s="7">
+      <c r="Y25" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Z25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AA25" s="7">
+      <c r="AA25" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AB25" s="6">
         <v>1.0</v>
       </c>
-      <c r="AC25" s="7">
+      <c r="AC25" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AD25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AE25" s="7">
+      <c r="AE25" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AF25" s="6">
         <v>2.0</v>
       </c>
-      <c r="AG25" s="7">
+      <c r="AG25" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AH25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AI25" s="7">
+      <c r="AI25" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AJ25" s="6">
         <v>1.0</v>
       </c>
-      <c r="AK25" s="7">
+      <c r="AK25" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AL25" s="6">
         <v>1.0</v>
       </c>
-      <c r="AM25" s="7">
+      <c r="AM25" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AN25" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO25" s="7">
+      <c r="AO25" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AP25" s="6">
         <v>2.0</v>
       </c>
-      <c r="AQ25" s="7">
+      <c r="AQ25" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR25" s="6">
         <v>2.0</v>
       </c>
-      <c r="AS25" s="7">
+      <c r="AS25" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT25" s="6">
         <v>1.0</v>
       </c>
-      <c r="AU25" s="7">
+      <c r="AU25" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AV25" s="6">
         <v>1.0</v>
       </c>
-      <c r="AW25" s="7">
+      <c r="AW25" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="26" ht="18.0" customHeight="1">
@@ -61680,7 +61634,7 @@
       </c>
       <c r="C5" s="19">
         <f>'Previsioni partecipanti'!I1</f>
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
@@ -61691,7 +61645,7 @@
       </c>
       <c r="C6" s="19">
         <f>'Previsioni partecipanti'!K1</f>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -61702,7 +61656,7 @@
       </c>
       <c r="C7" s="19">
         <f>'Previsioni partecipanti'!M1</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -61713,7 +61667,7 @@
       </c>
       <c r="C8" s="19">
         <f>'Previsioni partecipanti'!O1</f>
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
@@ -61724,7 +61678,7 @@
       </c>
       <c r="C9" s="19">
         <f>'Previsioni partecipanti'!Q1</f>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
@@ -61735,7 +61689,7 @@
       </c>
       <c r="C10" s="19">
         <f>'Previsioni partecipanti'!S1</f>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
@@ -61746,7 +61700,7 @@
       </c>
       <c r="C11" s="19">
         <f>'Previsioni partecipanti'!U1</f>
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
@@ -61757,7 +61711,7 @@
       </c>
       <c r="C12" s="19">
         <f>'Previsioni partecipanti'!W1</f>
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
@@ -61768,7 +61722,7 @@
       </c>
       <c r="C13" s="19">
         <f>'Previsioni partecipanti'!Y1</f>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
@@ -61779,7 +61733,7 @@
       </c>
       <c r="C14" s="19">
         <f>'Previsioni partecipanti'!AA1</f>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
@@ -61790,7 +61744,7 @@
       </c>
       <c r="C15" s="19">
         <f>'Previsioni partecipanti'!AC1</f>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
@@ -61801,7 +61755,7 @@
       </c>
       <c r="C16" s="19">
         <f>'Previsioni partecipanti'!AE1</f>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -61812,7 +61766,7 @@
       </c>
       <c r="C17" s="19">
         <f>'Previsioni partecipanti'!AG1</f>
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
@@ -61823,7 +61777,7 @@
       </c>
       <c r="C18" s="19">
         <f>'Previsioni partecipanti'!AI1</f>
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
@@ -61834,7 +61788,7 @@
       </c>
       <c r="C19" s="19">
         <f>'Previsioni partecipanti'!AK1</f>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -61845,7 +61799,7 @@
       </c>
       <c r="C20" s="19">
         <f>'Previsioni partecipanti'!AM1</f>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
@@ -61856,7 +61810,7 @@
       </c>
       <c r="C21" s="19">
         <f>'Previsioni partecipanti'!AO1</f>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
@@ -61867,7 +61821,7 @@
       </c>
       <c r="C22" s="19">
         <f>'Previsioni partecipanti'!AQ1</f>
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
@@ -61878,7 +61832,7 @@
       </c>
       <c r="C23" s="19">
         <f>'Previsioni partecipanti'!AS1</f>
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
@@ -61889,7 +61843,7 @@
       </c>
       <c r="C24" s="19">
         <f>'Previsioni partecipanti'!AU1</f>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
@@ -61900,7 +61854,7 @@
       </c>
       <c r="C25" s="19">
         <f>'Previsioni partecipanti'!AW1</f>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
@@ -64875,11 +64829,11 @@
       </c>
       <c r="B3" s="21" t="str">
         <f t="array" ref="B3">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B2,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,1),1,0),0)),"")</f>
-        <v>Marco G.</v>
+        <v>Leo Proietti</v>
       </c>
       <c r="C3" s="1">
         <f t="array" ref="C3">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B3,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>130</v>
@@ -64891,11 +64845,11 @@
       </c>
       <c r="B4" s="21" t="str">
         <f t="array" ref="B4">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B3,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,2),1,0),0)),"")</f>
-        <v>Valerio</v>
+        <v>Jack</v>
       </c>
       <c r="C4" s="1">
         <f t="array" ref="C4">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B4,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3"/>
     </row>
@@ -64905,11 +64859,11 @@
       </c>
       <c r="B5" s="21" t="str">
         <f t="array" ref="B5">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B4,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,3),1,0),0)),"")</f>
-        <v>Pier</v>
+        <v>Antonella</v>
       </c>
       <c r="C5" s="1">
         <f t="array" ref="C5">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B5,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -64919,11 +64873,11 @@
       </c>
       <c r="B6" s="21" t="str">
         <f t="array" ref="B6">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B5,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,4),1,0),0)),"")</f>
-        <v>Khawla</v>
+        <v>Vito</v>
       </c>
       <c r="C6" s="1">
         <f t="array" ref="C6">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B6,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3"/>
     </row>
@@ -64933,11 +64887,11 @@
       </c>
       <c r="B7" s="21" t="str">
         <f t="array" ref="B7">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B6,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,5),1,0),0)),"")</f>
-        <v>Leo Policella</v>
+        <v>Samuele</v>
       </c>
       <c r="C7" s="1">
         <f t="array" ref="C7">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B7,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1"/>
     </row>
@@ -64947,11 +64901,11 @@
       </c>
       <c r="B8" s="21" t="str">
         <f t="array" ref="B8">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B7,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,6),1,0),0)),"")</f>
-        <v>Edoardo</v>
+        <v>Valerio</v>
       </c>
       <c r="C8" s="1">
         <f t="array" ref="C8">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B8,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3"/>
     </row>
@@ -64961,11 +64915,11 @@
       </c>
       <c r="B9" s="21" t="str">
         <f t="array" ref="B9">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B8,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,7),1,0),0)),"")</f>
-        <v>Tania</v>
+        <v>Edoardo</v>
       </c>
       <c r="C9" s="1">
         <f t="array" ref="C9">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B9,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D9" s="1"/>
     </row>
@@ -64975,11 +64929,11 @@
       </c>
       <c r="B10" s="21" t="str">
         <f t="array" ref="B10">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B9,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,8),1,0),0)),"")</f>
-        <v>Alessio S.</v>
+        <v>Tania</v>
       </c>
       <c r="C10" s="1">
         <f t="array" ref="C10">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B10,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D10" s="3"/>
     </row>
@@ -64989,11 +64943,11 @@
       </c>
       <c r="B11" s="21" t="str">
         <f t="array" ref="B11">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B10,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,9),1,0),0)),"")</f>
-        <v>Claudia S.</v>
+        <v>Pier</v>
       </c>
       <c r="C11" s="1">
         <f t="array" ref="C11">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B11,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D11" s="1"/>
     </row>
@@ -65003,11 +64957,11 @@
       </c>
       <c r="B12" s="21" t="str">
         <f t="array" ref="B12">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B11,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,10),1,0),0)),"")</f>
-        <v>Jack</v>
+        <v>Alessandra C.</v>
       </c>
       <c r="C12" s="1">
         <f t="array" ref="C12">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B12,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D12" s="3"/>
     </row>
@@ -65017,11 +64971,11 @@
       </c>
       <c r="B13" s="21" t="str">
         <f t="array" ref="B13">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B12,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,11),1,0),0)),"")</f>
-        <v>Samuele</v>
+        <v>Alessandra P.</v>
       </c>
       <c r="C13" s="1">
         <f t="array" ref="C13">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B13,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D13" s="1"/>
     </row>
@@ -65031,11 +64985,11 @@
       </c>
       <c r="B14" s="21" t="str">
         <f t="array" ref="B14">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B13,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,12),1,0),0)),"")</f>
-        <v>Alessandra P.</v>
+        <v>Claudia A.</v>
       </c>
       <c r="C14" s="1">
         <f t="array" ref="C14">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B14,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D14" s="3"/>
     </row>
@@ -65045,11 +64999,11 @@
       </c>
       <c r="B15" s="21" t="str">
         <f t="array" ref="B15">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B14,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,13),1,0),0)),"")</f>
-        <v>Alessio R.</v>
+        <v>Marco G.</v>
       </c>
       <c r="C15" s="1">
         <f t="array" ref="C15">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B15,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D15" s="1"/>
     </row>
@@ -65059,11 +65013,11 @@
       </c>
       <c r="B16" s="21" t="str">
         <f t="array" ref="B16">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B15,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,14),1,0),0)),"")</f>
-        <v>Marco P.</v>
+        <v>Alessio S.</v>
       </c>
       <c r="C16" s="1">
         <f t="array" ref="C16">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B16,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D16" s="3"/>
     </row>
@@ -65073,11 +65027,11 @@
       </c>
       <c r="B17" s="21" t="str">
         <f t="array" ref="B17">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B16,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,15),1,0),0)),"")</f>
-        <v>Maila</v>
+        <v>Alessio R.</v>
       </c>
       <c r="C17" s="1">
         <f t="array" ref="C17">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B17,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D17" s="1"/>
     </row>
@@ -65087,11 +65041,11 @@
       </c>
       <c r="B18" s="21" t="str">
         <f t="array" ref="B18">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B17,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,16),1,0),0)),"")</f>
-        <v>Leo Proietti</v>
+        <v>Marco P.</v>
       </c>
       <c r="C18" s="1">
         <f t="array" ref="C18">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B18,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D18" s="3"/>
     </row>
@@ -65101,11 +65055,11 @@
       </c>
       <c r="B19" s="21" t="str">
         <f t="array" ref="B19">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B18,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,17),1,0),0)),"")</f>
-        <v>Vito</v>
+        <v>Khawla</v>
       </c>
       <c r="C19" s="1">
         <f t="array" ref="C19">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B19,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D19" s="1"/>
     </row>
@@ -65119,7 +65073,7 @@
       </c>
       <c r="C20" s="1">
         <f t="array" ref="C20">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B20,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D20" s="3"/>
     </row>
@@ -65129,11 +65083,11 @@
       </c>
       <c r="B21" s="21" t="str">
         <f t="array" ref="B21">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B20,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,19),1,0),0)),"")</f>
-        <v>Alessandra C.</v>
+        <v>Claudia S.</v>
       </c>
       <c r="C21" s="1">
         <f t="array" ref="C21">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B21,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D21" s="1"/>
     </row>
@@ -65143,11 +65097,11 @@
       </c>
       <c r="B22" s="21" t="str">
         <f t="array" ref="B22">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B21,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,20),1,0),0)),"")</f>
-        <v>Claudia A.</v>
+        <v>Leo Policella</v>
       </c>
       <c r="C22" s="1">
         <f t="array" ref="C22">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B22,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D22" s="3"/>
     </row>
@@ -65157,11 +65111,11 @@
       </c>
       <c r="B23" s="21" t="str">
         <f t="array" ref="B23">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B22,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,21),1,0),0)),"")</f>
-        <v>Antonella</v>
+        <v>Maila</v>
       </c>
       <c r="C23" s="1">
         <f t="array" ref="C23">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B23,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D23" s="1"/>
     </row>

--- a/html-files/DEF_Mondiali_2026_MASTER.xlsx
+++ b/html-files/DEF_Mondiali_2026_MASTER.xlsx
@@ -873,21 +873,21 @@
       </c>
       <c r="I1" s="1">
         <f>SUM(I3:I74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="1">
         <f>SUM(K3:K74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="1">
         <f>SUM(M3:M74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>10</v>
@@ -901,35 +901,35 @@
       </c>
       <c r="Q1" s="1">
         <f>SUM(Q3:Q74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="S1" s="1">
         <f>SUM(S3:S74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="U1" s="1">
         <f>SUM(U3:U74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V1" s="2" t="s">
         <v>14</v>
       </c>
       <c r="W1" s="1">
         <f>SUM(W3:W74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X1" s="2" t="s">
         <v>15</v>
       </c>
       <c r="Y1" s="1">
         <f>SUM(Y3:Y74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z1" s="2" t="s">
         <v>16</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="AE1" s="1">
         <f>SUM(AE3:AE74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF1" s="2" t="s">
         <v>19</v>
@@ -964,56 +964,56 @@
       </c>
       <c r="AI1" s="1">
         <f>SUM(AI3:AI74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ1" s="2" t="s">
         <v>21</v>
       </c>
       <c r="AK1" s="1">
         <f>SUM(AK3:AK74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL1" s="2" t="s">
         <v>22</v>
       </c>
       <c r="AM1" s="1">
         <f>SUM(AM3:AM74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN1" s="2" t="s">
         <v>23</v>
       </c>
       <c r="AO1" s="1">
         <f>SUM(AO3:AO74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="AQ1" s="1">
         <f>SUM(AQ3:AQ74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR1" s="2" t="s">
         <v>25</v>
       </c>
       <c r="AS1" s="1">
         <f>SUM(AS3:AS74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT1" s="2" t="s">
         <v>26</v>
       </c>
       <c r="AU1" s="1">
         <f>SUM(AU3:AU74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV1" s="2" t="s">
         <v>27</v>
       </c>
       <c r="AW1" s="1">
         <f>SUM(AW3:AW74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" ht="21.75" customHeight="1">
@@ -1172,153 +1172,155 @@
       <c r="F3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="5"/>
+      <c r="G3" s="5">
+        <v>1.0</v>
+      </c>
       <c r="H3" s="6">
         <v>1.0</v>
       </c>
-      <c r="I3" s="7" t="str">
+      <c r="I3" s="7">
         <f t="shared" ref="I3:I74" si="1">IF($G3&lt;&gt;"",IF(H3=$G3,1,0),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J3" s="6">
         <v>1.0</v>
       </c>
-      <c r="K3" s="7" t="str">
+      <c r="K3" s="7">
         <f t="shared" ref="K3:K74" si="2">IF($G3&lt;&gt;"",IF(J3=$G3,1,0),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L3" s="6">
         <v>1.0</v>
       </c>
-      <c r="M3" s="7" t="str">
+      <c r="M3" s="7">
         <f t="shared" ref="M3:M74" si="3">IF($G3&lt;&gt;"",IF(L3=$G3,1,0),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="O3" s="7" t="str">
+      <c r="O3" s="7">
         <f t="shared" ref="O3:O74" si="4">IF($G3&lt;&gt;"",IF(N3=$G3,1,0),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P3" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q3" s="7" t="str">
+      <c r="Q3" s="7">
         <f t="shared" ref="Q3:Q74" si="5">IF($G3&lt;&gt;"",IF(P3=$G3,1,0),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="R3" s="6">
         <v>1.0</v>
       </c>
-      <c r="S3" s="7" t="str">
+      <c r="S3" s="7">
         <f t="shared" ref="S3:S74" si="6">IF($G3&lt;&gt;"",IF(R3=$G3,1,0),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T3" s="6">
         <v>1.0</v>
       </c>
-      <c r="U3" s="7" t="str">
+      <c r="U3" s="7">
         <f t="shared" ref="U3:U74" si="7">IF($G3&lt;&gt;"",IF(T3=$G3,1,0),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="V3" s="6">
         <v>1.0</v>
       </c>
-      <c r="W3" s="7" t="str">
+      <c r="W3" s="7">
         <f t="shared" ref="W3:W74" si="8">IF($G3&lt;&gt;"",IF(V3=$G3,1,0),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="X3" s="6">
         <v>1.0</v>
       </c>
-      <c r="Y3" s="7" t="str">
+      <c r="Y3" s="7">
         <f t="shared" ref="Y3:Y74" si="9">IF($G3&lt;&gt;"",IF(X3=$G3,1,0),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Z3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AA3" s="7" t="str">
+      <c r="AA3" s="7">
         <f t="shared" ref="AA3:AA74" si="10">IF($G3&lt;&gt;"",IF(Z3=$G3,1,0),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AB3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AC3" s="7" t="str">
+      <c r="AC3" s="7">
         <f t="shared" ref="AC3:AC74" si="11">IF($G3&lt;&gt;"",IF(AB3=$G3,1,0),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AE3" s="7" t="str">
+      <c r="AE3" s="7">
         <f t="shared" ref="AE3:AE74" si="12">IF($G3&lt;&gt;"",IF(AD3=$G3,1,0),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AF3" s="6">
         <v>2.0</v>
       </c>
-      <c r="AG3" s="7" t="str">
+      <c r="AG3" s="7">
         <f t="shared" ref="AG3:AG74" si="13">IF($G3&lt;&gt;"",IF(AF3=$G3,1,0),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AH3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AI3" s="7" t="str">
+      <c r="AI3" s="7">
         <f t="shared" ref="AI3:AI74" si="14">IF($G3&lt;&gt;"",IF(AH3=$G3,1,0),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AJ3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AK3" s="7" t="str">
+      <c r="AK3" s="7">
         <f t="shared" ref="AK3:AK74" si="15">IF($G3&lt;&gt;"",IF(AJ3=$G3,1,0),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AL3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AM3" s="7" t="str">
+      <c r="AM3" s="7">
         <f t="shared" ref="AM3:AM74" si="16">IF($G3&lt;&gt;"",IF(AL3=$G3,1,0),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AN3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO3" s="7" t="str">
+      <c r="AO3" s="7">
         <f t="shared" ref="AO3:AO74" si="17">IF($G3&lt;&gt;"",IF(AN3=$G3,1,0),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AP3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AQ3" s="7" t="str">
+      <c r="AQ3" s="7">
         <f t="shared" ref="AQ3:AQ74" si="18">IF($G3&lt;&gt;"",IF(AP3=$G3,1,0),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AR3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AS3" s="7" t="str">
+      <c r="AS3" s="7">
         <f t="shared" ref="AS3:AS74" si="19">IF($G3&lt;&gt;"",IF(AR3=$G3,1,0),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AT3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AU3" s="7" t="str">
+      <c r="AU3" s="7">
         <f t="shared" ref="AU3:AU74" si="20">IF($G3&lt;&gt;"",IF(AT3=$G3,1,0),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AV3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AW3" s="7" t="str">
+      <c r="AW3" s="7">
         <f t="shared" ref="AW3:AW74" si="21">IF($G3&lt;&gt;"",IF(AV3=$G3,1,0),"")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="18.0" customHeight="1">
@@ -61634,7 +61636,7 @@
       </c>
       <c r="C5" s="19">
         <f>'Previsioni partecipanti'!I1</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
@@ -61645,7 +61647,7 @@
       </c>
       <c r="C6" s="19">
         <f>'Previsioni partecipanti'!K1</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -61656,7 +61658,7 @@
       </c>
       <c r="C7" s="19">
         <f>'Previsioni partecipanti'!M1</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -61678,7 +61680,7 @@
       </c>
       <c r="C9" s="19">
         <f>'Previsioni partecipanti'!Q1</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
@@ -61689,7 +61691,7 @@
       </c>
       <c r="C10" s="19">
         <f>'Previsioni partecipanti'!S1</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
@@ -61700,7 +61702,7 @@
       </c>
       <c r="C11" s="19">
         <f>'Previsioni partecipanti'!U1</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
@@ -61711,7 +61713,7 @@
       </c>
       <c r="C12" s="19">
         <f>'Previsioni partecipanti'!W1</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
@@ -61722,7 +61724,7 @@
       </c>
       <c r="C13" s="19">
         <f>'Previsioni partecipanti'!Y1</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
@@ -61755,7 +61757,7 @@
       </c>
       <c r="C16" s="19">
         <f>'Previsioni partecipanti'!AE1</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -61777,7 +61779,7 @@
       </c>
       <c r="C18" s="19">
         <f>'Previsioni partecipanti'!AI1</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
@@ -61788,7 +61790,7 @@
       </c>
       <c r="C19" s="19">
         <f>'Previsioni partecipanti'!AK1</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -61799,7 +61801,7 @@
       </c>
       <c r="C20" s="19">
         <f>'Previsioni partecipanti'!AM1</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
@@ -61810,7 +61812,7 @@
       </c>
       <c r="C21" s="19">
         <f>'Previsioni partecipanti'!AO1</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
@@ -61821,7 +61823,7 @@
       </c>
       <c r="C22" s="19">
         <f>'Previsioni partecipanti'!AQ1</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
@@ -61832,7 +61834,7 @@
       </c>
       <c r="C23" s="19">
         <f>'Previsioni partecipanti'!AS1</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
@@ -61843,7 +61845,7 @@
       </c>
       <c r="C24" s="19">
         <f>'Previsioni partecipanti'!AU1</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
@@ -61854,7 +61856,7 @@
       </c>
       <c r="C25" s="19">
         <f>'Previsioni partecipanti'!AW1</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
@@ -64833,7 +64835,7 @@
       </c>
       <c r="C3" s="1">
         <f t="array" ref="C3">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B3,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>130</v>
@@ -64849,7 +64851,7 @@
       </c>
       <c r="C4" s="1">
         <f t="array" ref="C4">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B4,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3"/>
     </row>
@@ -64863,7 +64865,7 @@
       </c>
       <c r="C5" s="1">
         <f t="array" ref="C5">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B5,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -64873,11 +64875,11 @@
       </c>
       <c r="B6" s="21" t="str">
         <f t="array" ref="B6">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B5,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,4),1,0),0)),"")</f>
-        <v>Vito</v>
+        <v>Samuele</v>
       </c>
       <c r="C6" s="1">
         <f t="array" ref="C6">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B6,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="3"/>
     </row>
@@ -64887,11 +64889,11 @@
       </c>
       <c r="B7" s="21" t="str">
         <f t="array" ref="B7">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B6,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,5),1,0),0)),"")</f>
-        <v>Samuele</v>
+        <v>Valerio</v>
       </c>
       <c r="C7" s="1">
         <f t="array" ref="C7">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B7,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1"/>
     </row>
@@ -64901,11 +64903,11 @@
       </c>
       <c r="B8" s="21" t="str">
         <f t="array" ref="B8">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B7,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,6),1,0),0)),"")</f>
-        <v>Valerio</v>
+        <v>Edoardo</v>
       </c>
       <c r="C8" s="1">
         <f t="array" ref="C8">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B8,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="3"/>
     </row>
@@ -64915,11 +64917,11 @@
       </c>
       <c r="B9" s="21" t="str">
         <f t="array" ref="B9">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B8,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,7),1,0),0)),"")</f>
-        <v>Edoardo</v>
+        <v>Tania</v>
       </c>
       <c r="C9" s="1">
         <f t="array" ref="C9">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B9,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1"/>
     </row>
@@ -64929,11 +64931,11 @@
       </c>
       <c r="B10" s="21" t="str">
         <f t="array" ref="B10">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B9,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,8),1,0),0)),"")</f>
-        <v>Tania</v>
+        <v>Pier</v>
       </c>
       <c r="C10" s="1">
         <f t="array" ref="C10">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B10,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="3"/>
     </row>
@@ -64943,11 +64945,11 @@
       </c>
       <c r="B11" s="21" t="str">
         <f t="array" ref="B11">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B10,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,9),1,0),0)),"")</f>
-        <v>Pier</v>
+        <v>Claudia A.</v>
       </c>
       <c r="C11" s="1">
         <f t="array" ref="C11">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B11,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="1"/>
     </row>
@@ -64957,11 +64959,11 @@
       </c>
       <c r="B12" s="21" t="str">
         <f t="array" ref="B12">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B11,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,10),1,0),0)),"")</f>
-        <v>Alessandra C.</v>
+        <v>Alessio S.</v>
       </c>
       <c r="C12" s="1">
         <f t="array" ref="C12">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B12,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="3"/>
     </row>
@@ -64971,11 +64973,11 @@
       </c>
       <c r="B13" s="21" t="str">
         <f t="array" ref="B13">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B12,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,11),1,0),0)),"")</f>
-        <v>Alessandra P.</v>
+        <v>Alessio R.</v>
       </c>
       <c r="C13" s="1">
         <f t="array" ref="C13">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B13,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="1"/>
     </row>
@@ -64985,11 +64987,11 @@
       </c>
       <c r="B14" s="21" t="str">
         <f t="array" ref="B14">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B13,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,12),1,0),0)),"")</f>
-        <v>Claudia A.</v>
+        <v>Marco P.</v>
       </c>
       <c r="C14" s="1">
         <f t="array" ref="C14">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B14,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="3"/>
     </row>
@@ -64999,11 +65001,11 @@
       </c>
       <c r="B15" s="21" t="str">
         <f t="array" ref="B15">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B14,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,13),1,0),0)),"")</f>
-        <v>Marco G.</v>
+        <v>Khawla</v>
       </c>
       <c r="C15" s="1">
         <f t="array" ref="C15">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B15,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="1"/>
     </row>
@@ -65013,11 +65015,11 @@
       </c>
       <c r="B16" s="21" t="str">
         <f t="array" ref="B16">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B15,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,14),1,0),0)),"")</f>
-        <v>Alessio S.</v>
+        <v>Federico R.</v>
       </c>
       <c r="C16" s="1">
         <f t="array" ref="C16">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B16,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="3"/>
     </row>
@@ -65027,11 +65029,11 @@
       </c>
       <c r="B17" s="21" t="str">
         <f t="array" ref="B17">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B16,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,15),1,0),0)),"")</f>
-        <v>Alessio R.</v>
+        <v>Claudia S.</v>
       </c>
       <c r="C17" s="1">
         <f t="array" ref="C17">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B17,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="1"/>
     </row>
@@ -65041,11 +65043,11 @@
       </c>
       <c r="B18" s="21" t="str">
         <f t="array" ref="B18">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B17,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,16),1,0),0)),"")</f>
-        <v>Marco P.</v>
+        <v>Leo Policella</v>
       </c>
       <c r="C18" s="1">
         <f t="array" ref="C18">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B18,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="3"/>
     </row>
@@ -65055,11 +65057,11 @@
       </c>
       <c r="B19" s="21" t="str">
         <f t="array" ref="B19">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B18,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,17),1,0),0)),"")</f>
-        <v>Khawla</v>
+        <v>Maila</v>
       </c>
       <c r="C19" s="1">
         <f t="array" ref="C19">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B19,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="1"/>
     </row>
@@ -65069,7 +65071,7 @@
       </c>
       <c r="B20" s="21" t="str">
         <f t="array" ref="B20">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B19,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,18),1,0),0)),"")</f>
-        <v>Federico R.</v>
+        <v>Vito</v>
       </c>
       <c r="C20" s="1">
         <f t="array" ref="C20">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B20,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65083,7 +65085,7 @@
       </c>
       <c r="B21" s="21" t="str">
         <f t="array" ref="B21">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B20,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,19),1,0),0)),"")</f>
-        <v>Claudia S.</v>
+        <v>Alessandra C.</v>
       </c>
       <c r="C21" s="1">
         <f t="array" ref="C21">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B21,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65097,7 +65099,7 @@
       </c>
       <c r="B22" s="21" t="str">
         <f t="array" ref="B22">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B21,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,20),1,0),0)),"")</f>
-        <v>Leo Policella</v>
+        <v>Alessandra P.</v>
       </c>
       <c r="C22" s="1">
         <f t="array" ref="C22">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B22,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65111,7 +65113,7 @@
       </c>
       <c r="B23" s="21" t="str">
         <f t="array" ref="B23">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B22,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,21),1,0),0)),"")</f>
-        <v>Maila</v>
+        <v>Marco G.</v>
       </c>
       <c r="C23" s="1">
         <f t="array" ref="C23">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B23,Elenco!$B$5:$B$25,0)),"")</f>

--- a/html-files/DEF_Mondiali_2026_MASTER.xlsx
+++ b/html-files/DEF_Mondiali_2026_MASTER.xlsx
@@ -880,21 +880,21 @@
       </c>
       <c r="K1" s="1">
         <f>SUM(K3:K74)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="1">
         <f>SUM(M3:M74)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="O1" s="1">
         <f>SUM(O3:O74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>11</v>
@@ -936,7 +936,7 @@
       </c>
       <c r="AA1" s="1">
         <f>SUM(AA3:AA74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB1" s="2" t="s">
         <v>17</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="AE1" s="1">
         <f>SUM(AE3:AE74)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF1" s="2" t="s">
         <v>19</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="AS1" s="1">
         <f>SUM(AS3:AS74)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT1" s="2" t="s">
         <v>26</v>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AW1" s="1">
         <f>SUM(AW3:AW74)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" ht="21.75" customHeight="1">
@@ -1342,153 +1342,155 @@
       <c r="F4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="5">
+        <v>2.0</v>
+      </c>
       <c r="H4" s="6">
         <v>1.0</v>
       </c>
-      <c r="I4" s="7" t="str">
+      <c r="I4" s="7">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J4" s="6">
         <v>2.0</v>
       </c>
-      <c r="K4" s="7" t="str">
+      <c r="K4" s="7">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L4" s="6">
         <v>2.0</v>
       </c>
-      <c r="M4" s="7" t="str">
+      <c r="M4" s="7">
         <f t="shared" si="3"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N4" s="6">
         <v>2.0</v>
       </c>
-      <c r="O4" s="7" t="str">
+      <c r="O4" s="7">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="P4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="Q4" s="7" t="str">
+      <c r="Q4" s="7">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="S4" s="7" t="str">
+      <c r="S4" s="7">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="U4" s="7" t="str">
+      <c r="U4" s="7">
         <f t="shared" si="7"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="V4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="W4" s="7" t="str">
+      <c r="W4" s="7">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X4" s="6">
         <v>1.0</v>
       </c>
-      <c r="Y4" s="7" t="str">
+      <c r="Y4" s="7">
         <f t="shared" si="9"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Z4" s="6">
         <v>2.0</v>
       </c>
-      <c r="AA4" s="7" t="str">
+      <c r="AA4" s="7">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AB4" s="6">
         <v>1.0</v>
       </c>
-      <c r="AC4" s="7" t="str">
+      <c r="AC4" s="7">
         <f t="shared" si="11"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD4" s="6">
         <v>2.0</v>
       </c>
-      <c r="AE4" s="7" t="str">
+      <c r="AE4" s="7">
         <f t="shared" si="12"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AF4" s="6">
         <v>1.0</v>
       </c>
-      <c r="AG4" s="7" t="str">
+      <c r="AG4" s="7">
         <f t="shared" si="13"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AH4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AI4" s="7" t="str">
+      <c r="AI4" s="7">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AJ4" s="6">
         <v>1.0</v>
       </c>
-      <c r="AK4" s="7" t="str">
+      <c r="AK4" s="7">
         <f t="shared" si="15"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL4" s="6">
         <v>1.0</v>
       </c>
-      <c r="AM4" s="7" t="str">
+      <c r="AM4" s="7">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AN4" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO4" s="7" t="str">
+      <c r="AO4" s="7">
         <f t="shared" si="17"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AP4" s="6">
         <v>1.0</v>
       </c>
-      <c r="AQ4" s="7" t="str">
+      <c r="AQ4" s="7">
         <f t="shared" si="18"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AR4" s="6">
         <v>2.0</v>
       </c>
-      <c r="AS4" s="7" t="str">
+      <c r="AS4" s="7">
         <f t="shared" si="19"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AT4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AU4" s="7" t="str">
+      <c r="AU4" s="7">
         <f t="shared" si="20"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AV4" s="6">
         <v>2.0</v>
       </c>
-      <c r="AW4" s="7" t="str">
+      <c r="AW4" s="7">
         <f t="shared" si="21"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="18.0" customHeight="1">
@@ -61647,7 +61649,7 @@
       </c>
       <c r="C6" s="19">
         <f>'Previsioni partecipanti'!K1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -61658,7 +61660,7 @@
       </c>
       <c r="C7" s="19">
         <f>'Previsioni partecipanti'!M1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -61669,7 +61671,7 @@
       </c>
       <c r="C8" s="19">
         <f>'Previsioni partecipanti'!O1</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
@@ -61735,7 +61737,7 @@
       </c>
       <c r="C14" s="19">
         <f>'Previsioni partecipanti'!AA1</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
@@ -61757,7 +61759,7 @@
       </c>
       <c r="C16" s="19">
         <f>'Previsioni partecipanti'!AE1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -61834,7 +61836,7 @@
       </c>
       <c r="C23" s="19">
         <f>'Previsioni partecipanti'!AS1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
@@ -61856,7 +61858,7 @@
       </c>
       <c r="C25" s="19">
         <f>'Previsioni partecipanti'!AW1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
@@ -64831,11 +64833,11 @@
       </c>
       <c r="B3" s="21" t="str">
         <f t="array" ref="B3">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B2,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,1),1,0),0)),"")</f>
-        <v>Leo Proietti</v>
+        <v>Jack</v>
       </c>
       <c r="C3" s="1">
         <f t="array" ref="C3">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B3,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>130</v>
@@ -64847,11 +64849,11 @@
       </c>
       <c r="B4" s="21" t="str">
         <f t="array" ref="B4">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B3,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,2),1,0),0)),"")</f>
-        <v>Jack</v>
+        <v>Antonella</v>
       </c>
       <c r="C4" s="1">
         <f t="array" ref="C4">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B4,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3"/>
     </row>
@@ -64861,11 +64863,11 @@
       </c>
       <c r="B5" s="21" t="str">
         <f t="array" ref="B5">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B4,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,3),1,0),0)),"")</f>
-        <v>Antonella</v>
+        <v>Claudia A.</v>
       </c>
       <c r="C5" s="1">
         <f t="array" ref="C5">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B5,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -64875,11 +64877,11 @@
       </c>
       <c r="B6" s="21" t="str">
         <f t="array" ref="B6">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B5,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,4),1,0),0)),"")</f>
-        <v>Samuele</v>
+        <v>Claudia S.</v>
       </c>
       <c r="C6" s="1">
         <f t="array" ref="C6">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B6,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="3"/>
     </row>
@@ -64889,11 +64891,11 @@
       </c>
       <c r="B7" s="21" t="str">
         <f t="array" ref="B7">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B6,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,5),1,0),0)),"")</f>
-        <v>Valerio</v>
+        <v>Maila</v>
       </c>
       <c r="C7" s="1">
         <f t="array" ref="C7">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B7,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="1"/>
     </row>
@@ -64903,7 +64905,7 @@
       </c>
       <c r="B8" s="21" t="str">
         <f t="array" ref="B8">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B7,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,6),1,0),0)),"")</f>
-        <v>Edoardo</v>
+        <v>Leo Proietti</v>
       </c>
       <c r="C8" s="1">
         <f t="array" ref="C8">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B8,Elenco!$B$5:$B$25,0)),"")</f>
@@ -64917,7 +64919,7 @@
       </c>
       <c r="B9" s="21" t="str">
         <f t="array" ref="B9">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B8,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,7),1,0),0)),"")</f>
-        <v>Tania</v>
+        <v>Vito</v>
       </c>
       <c r="C9" s="1">
         <f t="array" ref="C9">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B9,Elenco!$B$5:$B$25,0)),"")</f>
@@ -64931,7 +64933,7 @@
       </c>
       <c r="B10" s="21" t="str">
         <f t="array" ref="B10">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B9,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,8),1,0),0)),"")</f>
-        <v>Pier</v>
+        <v>Samuele</v>
       </c>
       <c r="C10" s="1">
         <f t="array" ref="C10">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B10,Elenco!$B$5:$B$25,0)),"")</f>
@@ -64945,7 +64947,7 @@
       </c>
       <c r="B11" s="21" t="str">
         <f t="array" ref="B11">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B10,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,9),1,0),0)),"")</f>
-        <v>Claudia A.</v>
+        <v>Valerio</v>
       </c>
       <c r="C11" s="1">
         <f t="array" ref="C11">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B11,Elenco!$B$5:$B$25,0)),"")</f>
@@ -64959,7 +64961,7 @@
       </c>
       <c r="B12" s="21" t="str">
         <f t="array" ref="B12">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B11,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,10),1,0),0)),"")</f>
-        <v>Alessio S.</v>
+        <v>Edoardo</v>
       </c>
       <c r="C12" s="1">
         <f t="array" ref="C12">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B12,Elenco!$B$5:$B$25,0)),"")</f>
@@ -64973,7 +64975,7 @@
       </c>
       <c r="B13" s="21" t="str">
         <f t="array" ref="B13">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B12,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,11),1,0),0)),"")</f>
-        <v>Alessio R.</v>
+        <v>Tania</v>
       </c>
       <c r="C13" s="1">
         <f t="array" ref="C13">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B13,Elenco!$B$5:$B$25,0)),"")</f>
@@ -64987,7 +64989,7 @@
       </c>
       <c r="B14" s="21" t="str">
         <f t="array" ref="B14">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B13,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,12),1,0),0)),"")</f>
-        <v>Marco P.</v>
+        <v>Pier</v>
       </c>
       <c r="C14" s="1">
         <f t="array" ref="C14">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B14,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65001,7 +65003,7 @@
       </c>
       <c r="B15" s="21" t="str">
         <f t="array" ref="B15">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B14,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,13),1,0),0)),"")</f>
-        <v>Khawla</v>
+        <v>Alessandra C.</v>
       </c>
       <c r="C15" s="1">
         <f t="array" ref="C15">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B15,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65015,7 +65017,7 @@
       </c>
       <c r="B16" s="21" t="str">
         <f t="array" ref="B16">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B15,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,14),1,0),0)),"")</f>
-        <v>Federico R.</v>
+        <v>Alessio S.</v>
       </c>
       <c r="C16" s="1">
         <f t="array" ref="C16">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B16,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65029,7 +65031,7 @@
       </c>
       <c r="B17" s="21" t="str">
         <f t="array" ref="B17">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B16,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,15),1,0),0)),"")</f>
-        <v>Claudia S.</v>
+        <v>Alessio R.</v>
       </c>
       <c r="C17" s="1">
         <f t="array" ref="C17">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B17,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65043,7 +65045,7 @@
       </c>
       <c r="B18" s="21" t="str">
         <f t="array" ref="B18">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B17,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,16),1,0),0)),"")</f>
-        <v>Leo Policella</v>
+        <v>Marco P.</v>
       </c>
       <c r="C18" s="1">
         <f t="array" ref="C18">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B18,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65057,7 +65059,7 @@
       </c>
       <c r="B19" s="21" t="str">
         <f t="array" ref="B19">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B18,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,17),1,0),0)),"")</f>
-        <v>Maila</v>
+        <v>Khawla</v>
       </c>
       <c r="C19" s="1">
         <f t="array" ref="C19">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B19,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65071,11 +65073,11 @@
       </c>
       <c r="B20" s="21" t="str">
         <f t="array" ref="B20">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B19,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,18),1,0),0)),"")</f>
-        <v>Vito</v>
+        <v>Federico R.</v>
       </c>
       <c r="C20" s="1">
         <f t="array" ref="C20">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B20,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="3"/>
     </row>
@@ -65085,11 +65087,11 @@
       </c>
       <c r="B21" s="21" t="str">
         <f t="array" ref="B21">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B20,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,19),1,0),0)),"")</f>
-        <v>Alessandra C.</v>
+        <v>Leo Policella</v>
       </c>
       <c r="C21" s="1">
         <f t="array" ref="C21">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B21,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" s="1"/>
     </row>

--- a/html-files/DEF_Mondiali_2026_MASTER.xlsx
+++ b/html-files/DEF_Mondiali_2026_MASTER.xlsx
@@ -873,21 +873,21 @@
       </c>
       <c r="I1" s="1">
         <f>SUM(I3:I74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="1">
         <f>SUM(K3:K74)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="1">
         <f>SUM(M3:M74)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>10</v>
@@ -901,35 +901,35 @@
       </c>
       <c r="Q1" s="1">
         <f>SUM(Q3:Q74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="S1" s="1">
         <f>SUM(S3:S74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="U1" s="1">
         <f>SUM(U3:U74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V1" s="2" t="s">
         <v>14</v>
       </c>
       <c r="W1" s="1">
         <f>SUM(W3:W74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X1" s="2" t="s">
         <v>15</v>
       </c>
       <c r="Y1" s="1">
         <f>SUM(Y3:Y74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z1" s="2" t="s">
         <v>16</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="AE1" s="1">
         <f>SUM(AE3:AE74)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF1" s="2" t="s">
         <v>19</v>
@@ -964,56 +964,56 @@
       </c>
       <c r="AI1" s="1">
         <f>SUM(AI3:AI74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ1" s="2" t="s">
         <v>21</v>
       </c>
       <c r="AK1" s="1">
         <f>SUM(AK3:AK74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL1" s="2" t="s">
         <v>22</v>
       </c>
       <c r="AM1" s="1">
         <f>SUM(AM3:AM74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN1" s="2" t="s">
         <v>23</v>
       </c>
       <c r="AO1" s="1">
         <f>SUM(AO3:AO74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="AQ1" s="1">
         <f>SUM(AQ3:AQ74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR1" s="2" t="s">
         <v>25</v>
       </c>
       <c r="AS1" s="1">
         <f>SUM(AS3:AS74)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT1" s="2" t="s">
         <v>26</v>
       </c>
       <c r="AU1" s="1">
         <f>SUM(AU3:AU74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV1" s="2" t="s">
         <v>27</v>
       </c>
       <c r="AW1" s="1">
         <f>SUM(AW3:AW74)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" ht="21.75" customHeight="1">
@@ -1172,155 +1172,153 @@
       <c r="F3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="5">
-        <v>1.0</v>
-      </c>
+      <c r="G3" s="5"/>
       <c r="H3" s="6">
         <v>1.0</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="7" t="str">
         <f t="shared" ref="I3:I74" si="1">IF($G3&lt;&gt;"",IF(H3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J3" s="6">
         <v>1.0</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="7" t="str">
         <f t="shared" ref="K3:K74" si="2">IF($G3&lt;&gt;"",IF(J3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="L3" s="6">
         <v>1.0</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="7" t="str">
         <f t="shared" ref="M3:M74" si="3">IF($G3&lt;&gt;"",IF(L3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="N3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="O3" s="7">
+      <c r="O3" s="7" t="str">
         <f t="shared" ref="O3:O74" si="4">IF($G3&lt;&gt;"",IF(N3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P3" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q3" s="7">
+      <c r="Q3" s="7" t="str">
         <f t="shared" ref="Q3:Q74" si="5">IF($G3&lt;&gt;"",IF(P3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="R3" s="6">
         <v>1.0</v>
       </c>
-      <c r="S3" s="7">
+      <c r="S3" s="7" t="str">
         <f t="shared" ref="S3:S74" si="6">IF($G3&lt;&gt;"",IF(R3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="T3" s="6">
         <v>1.0</v>
       </c>
-      <c r="U3" s="7">
+      <c r="U3" s="7" t="str">
         <f t="shared" ref="U3:U74" si="7">IF($G3&lt;&gt;"",IF(T3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="V3" s="6">
         <v>1.0</v>
       </c>
-      <c r="W3" s="7">
+      <c r="W3" s="7" t="str">
         <f t="shared" ref="W3:W74" si="8">IF($G3&lt;&gt;"",IF(V3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="X3" s="6">
         <v>1.0</v>
       </c>
-      <c r="Y3" s="7">
+      <c r="Y3" s="7" t="str">
         <f t="shared" ref="Y3:Y74" si="9">IF($G3&lt;&gt;"",IF(X3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Z3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AA3" s="7">
+      <c r="AA3" s="7" t="str">
         <f t="shared" ref="AA3:AA74" si="10">IF($G3&lt;&gt;"",IF(Z3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AB3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AC3" s="7">
+      <c r="AC3" s="7" t="str">
         <f t="shared" ref="AC3:AC74" si="11">IF($G3&lt;&gt;"",IF(AB3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AD3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AE3" s="7">
+      <c r="AE3" s="7" t="str">
         <f t="shared" ref="AE3:AE74" si="12">IF($G3&lt;&gt;"",IF(AD3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AF3" s="6">
         <v>2.0</v>
       </c>
-      <c r="AG3" s="7">
+      <c r="AG3" s="7" t="str">
         <f t="shared" ref="AG3:AG74" si="13">IF($G3&lt;&gt;"",IF(AF3=$G3,1,0),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AH3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AI3" s="7">
+      <c r="AI3" s="7" t="str">
         <f t="shared" ref="AI3:AI74" si="14">IF($G3&lt;&gt;"",IF(AH3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AJ3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AK3" s="7">
+      <c r="AK3" s="7" t="str">
         <f t="shared" ref="AK3:AK74" si="15">IF($G3&lt;&gt;"",IF(AJ3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AL3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AM3" s="7">
+      <c r="AM3" s="7" t="str">
         <f t="shared" ref="AM3:AM74" si="16">IF($G3&lt;&gt;"",IF(AL3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AN3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO3" s="7">
+      <c r="AO3" s="7" t="str">
         <f t="shared" ref="AO3:AO74" si="17">IF($G3&lt;&gt;"",IF(AN3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AP3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AQ3" s="7">
+      <c r="AQ3" s="7" t="str">
         <f t="shared" ref="AQ3:AQ74" si="18">IF($G3&lt;&gt;"",IF(AP3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AR3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AS3" s="7">
+      <c r="AS3" s="7" t="str">
         <f t="shared" ref="AS3:AS74" si="19">IF($G3&lt;&gt;"",IF(AR3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AT3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AU3" s="7">
+      <c r="AU3" s="7" t="str">
         <f t="shared" ref="AU3:AU74" si="20">IF($G3&lt;&gt;"",IF(AT3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AV3" s="6">
         <v>1.0</v>
       </c>
-      <c r="AW3" s="7">
+      <c r="AW3" s="7" t="str">
         <f t="shared" ref="AW3:AW74" si="21">IF($G3&lt;&gt;"",IF(AV3=$G3,1,0),"")</f>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="4" ht="18.0" customHeight="1">
@@ -61638,7 +61636,7 @@
       </c>
       <c r="C5" s="19">
         <f>'Previsioni partecipanti'!I1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
@@ -61649,7 +61647,7 @@
       </c>
       <c r="C6" s="19">
         <f>'Previsioni partecipanti'!K1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -61660,7 +61658,7 @@
       </c>
       <c r="C7" s="19">
         <f>'Previsioni partecipanti'!M1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -61682,7 +61680,7 @@
       </c>
       <c r="C9" s="19">
         <f>'Previsioni partecipanti'!Q1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
@@ -61693,7 +61691,7 @@
       </c>
       <c r="C10" s="19">
         <f>'Previsioni partecipanti'!S1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
@@ -61704,7 +61702,7 @@
       </c>
       <c r="C11" s="19">
         <f>'Previsioni partecipanti'!U1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
@@ -61715,7 +61713,7 @@
       </c>
       <c r="C12" s="19">
         <f>'Previsioni partecipanti'!W1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
@@ -61726,7 +61724,7 @@
       </c>
       <c r="C13" s="19">
         <f>'Previsioni partecipanti'!Y1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
@@ -61759,7 +61757,7 @@
       </c>
       <c r="C16" s="19">
         <f>'Previsioni partecipanti'!AE1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -61781,7 +61779,7 @@
       </c>
       <c r="C18" s="19">
         <f>'Previsioni partecipanti'!AI1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
@@ -61792,7 +61790,7 @@
       </c>
       <c r="C19" s="19">
         <f>'Previsioni partecipanti'!AK1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -61803,7 +61801,7 @@
       </c>
       <c r="C20" s="19">
         <f>'Previsioni partecipanti'!AM1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
@@ -61814,7 +61812,7 @@
       </c>
       <c r="C21" s="19">
         <f>'Previsioni partecipanti'!AO1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
@@ -61825,7 +61823,7 @@
       </c>
       <c r="C22" s="19">
         <f>'Previsioni partecipanti'!AQ1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
@@ -61836,7 +61834,7 @@
       </c>
       <c r="C23" s="19">
         <f>'Previsioni partecipanti'!AS1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
@@ -61847,7 +61845,7 @@
       </c>
       <c r="C24" s="19">
         <f>'Previsioni partecipanti'!AU1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
@@ -61858,7 +61856,7 @@
       </c>
       <c r="C25" s="19">
         <f>'Previsioni partecipanti'!AW1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
@@ -64837,7 +64835,7 @@
       </c>
       <c r="C3" s="1">
         <f t="array" ref="C3">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B3,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>130</v>
@@ -64853,7 +64851,7 @@
       </c>
       <c r="C4" s="1">
         <f t="array" ref="C4">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B4,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3"/>
     </row>
@@ -64863,11 +64861,11 @@
       </c>
       <c r="B5" s="21" t="str">
         <f t="array" ref="B5">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B4,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,3),1,0),0)),"")</f>
-        <v>Claudia A.</v>
+        <v>Vito</v>
       </c>
       <c r="C5" s="1">
         <f t="array" ref="C5">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B5,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -64877,11 +64875,11 @@
       </c>
       <c r="B6" s="21" t="str">
         <f t="array" ref="B6">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B5,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,4),1,0),0)),"")</f>
-        <v>Claudia S.</v>
+        <v>Alessandra C.</v>
       </c>
       <c r="C6" s="1">
         <f t="array" ref="C6">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B6,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="3"/>
     </row>
@@ -64891,11 +64889,11 @@
       </c>
       <c r="B7" s="21" t="str">
         <f t="array" ref="B7">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B6,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,5),1,0),0)),"")</f>
-        <v>Maila</v>
+        <v>Claudia A.</v>
       </c>
       <c r="C7" s="1">
         <f t="array" ref="C7">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B7,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1"/>
     </row>
@@ -64905,7 +64903,7 @@
       </c>
       <c r="B8" s="21" t="str">
         <f t="array" ref="B8">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B7,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,6),1,0),0)),"")</f>
-        <v>Leo Proietti</v>
+        <v>Claudia S.</v>
       </c>
       <c r="C8" s="1">
         <f t="array" ref="C8">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B8,Elenco!$B$5:$B$25,0)),"")</f>
@@ -64919,7 +64917,7 @@
       </c>
       <c r="B9" s="21" t="str">
         <f t="array" ref="B9">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B8,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,7),1,0),0)),"")</f>
-        <v>Vito</v>
+        <v>Maila</v>
       </c>
       <c r="C9" s="1">
         <f t="array" ref="C9">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B9,Elenco!$B$5:$B$25,0)),"")</f>
@@ -64933,11 +64931,11 @@
       </c>
       <c r="B10" s="21" t="str">
         <f t="array" ref="B10">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B9,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,8),1,0),0)),"")</f>
-        <v>Samuele</v>
+        <v>Leo Proietti</v>
       </c>
       <c r="C10" s="1">
         <f t="array" ref="C10">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B10,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="3"/>
     </row>
@@ -64947,11 +64945,11 @@
       </c>
       <c r="B11" s="21" t="str">
         <f t="array" ref="B11">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B10,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,9),1,0),0)),"")</f>
-        <v>Valerio</v>
+        <v>Samuele</v>
       </c>
       <c r="C11" s="1">
         <f t="array" ref="C11">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B11,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="1"/>
     </row>
@@ -64961,11 +64959,11 @@
       </c>
       <c r="B12" s="21" t="str">
         <f t="array" ref="B12">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B11,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,10),1,0),0)),"")</f>
-        <v>Edoardo</v>
+        <v>Valerio</v>
       </c>
       <c r="C12" s="1">
         <f t="array" ref="C12">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B12,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="3"/>
     </row>
@@ -64975,11 +64973,11 @@
       </c>
       <c r="B13" s="21" t="str">
         <f t="array" ref="B13">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B12,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,11),1,0),0)),"")</f>
-        <v>Tania</v>
+        <v>Edoardo</v>
       </c>
       <c r="C13" s="1">
         <f t="array" ref="C13">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B13,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="1"/>
     </row>
@@ -64989,11 +64987,11 @@
       </c>
       <c r="B14" s="21" t="str">
         <f t="array" ref="B14">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B13,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,12),1,0),0)),"")</f>
-        <v>Pier</v>
+        <v>Tania</v>
       </c>
       <c r="C14" s="1">
         <f t="array" ref="C14">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B14,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="3"/>
     </row>
@@ -65003,11 +65001,11 @@
       </c>
       <c r="B15" s="21" t="str">
         <f t="array" ref="B15">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B14,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,13),1,0),0)),"")</f>
-        <v>Alessandra C.</v>
+        <v>Pier</v>
       </c>
       <c r="C15" s="1">
         <f t="array" ref="C15">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B15,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="1"/>
     </row>
@@ -65017,11 +65015,11 @@
       </c>
       <c r="B16" s="21" t="str">
         <f t="array" ref="B16">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B15,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,14),1,0),0)),"")</f>
-        <v>Alessio S.</v>
+        <v>Alessandra P.</v>
       </c>
       <c r="C16" s="1">
         <f t="array" ref="C16">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B16,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="3"/>
     </row>
@@ -65031,11 +65029,11 @@
       </c>
       <c r="B17" s="21" t="str">
         <f t="array" ref="B17">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B16,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,15),1,0),0)),"")</f>
-        <v>Alessio R.</v>
+        <v>Marco G.</v>
       </c>
       <c r="C17" s="1">
         <f t="array" ref="C17">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B17,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="1"/>
     </row>
@@ -65045,11 +65043,11 @@
       </c>
       <c r="B18" s="21" t="str">
         <f t="array" ref="B18">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B17,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,16),1,0),0)),"")</f>
-        <v>Marco P.</v>
+        <v>Alessio S.</v>
       </c>
       <c r="C18" s="1">
         <f t="array" ref="C18">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B18,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="3"/>
     </row>
@@ -65059,11 +65057,11 @@
       </c>
       <c r="B19" s="21" t="str">
         <f t="array" ref="B19">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B18,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,17),1,0),0)),"")</f>
-        <v>Khawla</v>
+        <v>Alessio R.</v>
       </c>
       <c r="C19" s="1">
         <f t="array" ref="C19">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B19,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="1"/>
     </row>
@@ -65073,11 +65071,11 @@
       </c>
       <c r="B20" s="21" t="str">
         <f t="array" ref="B20">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B19,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,18),1,0),0)),"")</f>
-        <v>Federico R.</v>
+        <v>Marco P.</v>
       </c>
       <c r="C20" s="1">
         <f t="array" ref="C20">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B20,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="3"/>
     </row>
@@ -65087,11 +65085,11 @@
       </c>
       <c r="B21" s="21" t="str">
         <f t="array" ref="B21">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B20,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,19),1,0),0)),"")</f>
-        <v>Leo Policella</v>
+        <v>Khawla</v>
       </c>
       <c r="C21" s="1">
         <f t="array" ref="C21">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B21,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="1"/>
     </row>
@@ -65101,7 +65099,7 @@
       </c>
       <c r="B22" s="21" t="str">
         <f t="array" ref="B22">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B21,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,20),1,0),0)),"")</f>
-        <v>Alessandra P.</v>
+        <v>Federico R.</v>
       </c>
       <c r="C22" s="1">
         <f t="array" ref="C22">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B22,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65115,7 +65113,7 @@
       </c>
       <c r="B23" s="21" t="str">
         <f t="array" ref="B23">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B22,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,21),1,0),0)),"")</f>
-        <v>Marco G.</v>
+        <v>Leo Policella</v>
       </c>
       <c r="C23" s="1">
         <f t="array" ref="C23">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B23,Elenco!$B$5:$B$25,0)),"")</f>

--- a/html-files/DEF_Mondiali_2026_MASTER.xlsx
+++ b/html-files/DEF_Mondiali_2026_MASTER.xlsx
@@ -880,21 +880,21 @@
       </c>
       <c r="K1" s="1">
         <f>SUM(K3:K74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="1">
         <f>SUM(M3:M74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="O1" s="1">
         <f>SUM(O3:O74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>11</v>
@@ -936,7 +936,7 @@
       </c>
       <c r="AA1" s="1">
         <f>SUM(AA3:AA74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB1" s="2" t="s">
         <v>17</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="AE1" s="1">
         <f>SUM(AE3:AE74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF1" s="2" t="s">
         <v>19</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="AS1" s="1">
         <f>SUM(AS3:AS74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT1" s="2" t="s">
         <v>26</v>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AW1" s="1">
         <f>SUM(AW3:AW74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" ht="21.75" customHeight="1">
@@ -1340,155 +1340,153 @@
       <c r="F4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="5">
-        <v>2.0</v>
-      </c>
+      <c r="G4" s="5"/>
       <c r="H4" s="6">
         <v>1.0</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J4" s="6">
         <v>2.0</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="L4" s="6">
         <v>2.0</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="N4" s="6">
         <v>2.0</v>
       </c>
-      <c r="O4" s="7">
+      <c r="O4" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="P4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="Q4" s="7">
+      <c r="Q4" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="S4" s="7">
+      <c r="S4" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="U4" s="7">
+      <c r="U4" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="V4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="W4" s="7">
+      <c r="W4" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="X4" s="6">
         <v>1.0</v>
       </c>
-      <c r="Y4" s="7">
+      <c r="Y4" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Z4" s="6">
         <v>2.0</v>
       </c>
-      <c r="AA4" s="7">
+      <c r="AA4" s="7" t="str">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AB4" s="6">
         <v>1.0</v>
       </c>
-      <c r="AC4" s="7">
+      <c r="AC4" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AD4" s="6">
         <v>2.0</v>
       </c>
-      <c r="AE4" s="7">
+      <c r="AE4" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AF4" s="6">
         <v>1.0</v>
       </c>
-      <c r="AG4" s="7">
+      <c r="AG4" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AH4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AI4" s="7">
+      <c r="AI4" s="7" t="str">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AJ4" s="6">
         <v>1.0</v>
       </c>
-      <c r="AK4" s="7">
+      <c r="AK4" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL4" s="6">
         <v>1.0</v>
       </c>
-      <c r="AM4" s="7">
+      <c r="AM4" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AN4" s="6">
         <v>1.0</v>
       </c>
-      <c r="AO4" s="7">
+      <c r="AO4" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AP4" s="6">
         <v>1.0</v>
       </c>
-      <c r="AQ4" s="7">
+      <c r="AQ4" s="7" t="str">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR4" s="6">
         <v>2.0</v>
       </c>
-      <c r="AS4" s="7">
+      <c r="AS4" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AT4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AU4" s="7">
+      <c r="AU4" s="7" t="str">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AV4" s="6">
         <v>2.0</v>
       </c>
-      <c r="AW4" s="7">
+      <c r="AW4" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="5" ht="18.0" customHeight="1">
@@ -61647,7 +61645,7 @@
       </c>
       <c r="C6" s="19">
         <f>'Previsioni partecipanti'!K1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -61658,7 +61656,7 @@
       </c>
       <c r="C7" s="19">
         <f>'Previsioni partecipanti'!M1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -61669,7 +61667,7 @@
       </c>
       <c r="C8" s="19">
         <f>'Previsioni partecipanti'!O1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
@@ -61735,7 +61733,7 @@
       </c>
       <c r="C14" s="19">
         <f>'Previsioni partecipanti'!AA1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
@@ -61757,7 +61755,7 @@
       </c>
       <c r="C16" s="19">
         <f>'Previsioni partecipanti'!AE1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -61834,7 +61832,7 @@
       </c>
       <c r="C23" s="19">
         <f>'Previsioni partecipanti'!AS1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
@@ -61856,7 +61854,7 @@
       </c>
       <c r="C25" s="19">
         <f>'Previsioni partecipanti'!AW1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
@@ -64831,11 +64829,11 @@
       </c>
       <c r="B3" s="21" t="str">
         <f t="array" ref="B3">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B2,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,1),1,0),0)),"")</f>
-        <v>Jack</v>
+        <v>Leo Proietti</v>
       </c>
       <c r="C3" s="1">
         <f t="array" ref="C3">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B3,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>130</v>
@@ -64847,11 +64845,11 @@
       </c>
       <c r="B4" s="21" t="str">
         <f t="array" ref="B4">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B3,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,2),1,0),0)),"")</f>
-        <v>Antonella</v>
+        <v>Jack</v>
       </c>
       <c r="C4" s="1">
         <f t="array" ref="C4">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B4,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3"/>
     </row>
@@ -64861,11 +64859,11 @@
       </c>
       <c r="B5" s="21" t="str">
         <f t="array" ref="B5">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B4,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,3),1,0),0)),"")</f>
-        <v>Vito</v>
+        <v>Antonella</v>
       </c>
       <c r="C5" s="1">
         <f t="array" ref="C5">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B5,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -64875,11 +64873,11 @@
       </c>
       <c r="B6" s="21" t="str">
         <f t="array" ref="B6">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B5,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,4),1,0),0)),"")</f>
-        <v>Alessandra C.</v>
+        <v>Vito</v>
       </c>
       <c r="C6" s="1">
         <f t="array" ref="C6">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B6,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3"/>
     </row>
@@ -64889,11 +64887,11 @@
       </c>
       <c r="B7" s="21" t="str">
         <f t="array" ref="B7">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B6,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,5),1,0),0)),"")</f>
-        <v>Claudia A.</v>
+        <v>Samuele</v>
       </c>
       <c r="C7" s="1">
         <f t="array" ref="C7">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B7,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1"/>
     </row>
@@ -64903,11 +64901,11 @@
       </c>
       <c r="B8" s="21" t="str">
         <f t="array" ref="B8">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B7,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,6),1,0),0)),"")</f>
-        <v>Claudia S.</v>
+        <v>Valerio</v>
       </c>
       <c r="C8" s="1">
         <f t="array" ref="C8">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B8,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3"/>
     </row>
@@ -64917,11 +64915,11 @@
       </c>
       <c r="B9" s="21" t="str">
         <f t="array" ref="B9">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B8,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,7),1,0),0)),"")</f>
-        <v>Maila</v>
+        <v>Edoardo</v>
       </c>
       <c r="C9" s="1">
         <f t="array" ref="C9">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B9,Elenco!$B$5:$B$25,0)),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="1"/>
     </row>
@@ -64931,7 +64929,7 @@
       </c>
       <c r="B10" s="21" t="str">
         <f t="array" ref="B10">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B9,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,8),1,0),0)),"")</f>
-        <v>Leo Proietti</v>
+        <v>Tania</v>
       </c>
       <c r="C10" s="1">
         <f t="array" ref="C10">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B10,Elenco!$B$5:$B$25,0)),"")</f>
@@ -64945,7 +64943,7 @@
       </c>
       <c r="B11" s="21" t="str">
         <f t="array" ref="B11">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B10,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,9),1,0),0)),"")</f>
-        <v>Samuele</v>
+        <v>Pier</v>
       </c>
       <c r="C11" s="1">
         <f t="array" ref="C11">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B11,Elenco!$B$5:$B$25,0)),"")</f>
@@ -64959,7 +64957,7 @@
       </c>
       <c r="B12" s="21" t="str">
         <f t="array" ref="B12">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B11,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,10),1,0),0)),"")</f>
-        <v>Valerio</v>
+        <v>Alessandra C.</v>
       </c>
       <c r="C12" s="1">
         <f t="array" ref="C12">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B12,Elenco!$B$5:$B$25,0)),"")</f>
@@ -64973,7 +64971,7 @@
       </c>
       <c r="B13" s="21" t="str">
         <f t="array" ref="B13">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B12,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,11),1,0),0)),"")</f>
-        <v>Edoardo</v>
+        <v>Alessandra P.</v>
       </c>
       <c r="C13" s="1">
         <f t="array" ref="C13">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B13,Elenco!$B$5:$B$25,0)),"")</f>
@@ -64987,7 +64985,7 @@
       </c>
       <c r="B14" s="21" t="str">
         <f t="array" ref="B14">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B13,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,12),1,0),0)),"")</f>
-        <v>Tania</v>
+        <v>Claudia A.</v>
       </c>
       <c r="C14" s="1">
         <f t="array" ref="C14">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B14,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65001,7 +64999,7 @@
       </c>
       <c r="B15" s="21" t="str">
         <f t="array" ref="B15">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B14,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,13),1,0),0)),"")</f>
-        <v>Pier</v>
+        <v>Marco G.</v>
       </c>
       <c r="C15" s="1">
         <f t="array" ref="C15">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B15,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65015,7 +65013,7 @@
       </c>
       <c r="B16" s="21" t="str">
         <f t="array" ref="B16">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B15,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,14),1,0),0)),"")</f>
-        <v>Alessandra P.</v>
+        <v>Alessio S.</v>
       </c>
       <c r="C16" s="1">
         <f t="array" ref="C16">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B16,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65029,7 +65027,7 @@
       </c>
       <c r="B17" s="21" t="str">
         <f t="array" ref="B17">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B16,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,15),1,0),0)),"")</f>
-        <v>Marco G.</v>
+        <v>Alessio R.</v>
       </c>
       <c r="C17" s="1">
         <f t="array" ref="C17">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B17,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65043,7 +65041,7 @@
       </c>
       <c r="B18" s="21" t="str">
         <f t="array" ref="B18">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B17,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,16),1,0),0)),"")</f>
-        <v>Alessio S.</v>
+        <v>Marco P.</v>
       </c>
       <c r="C18" s="1">
         <f t="array" ref="C18">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B18,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65057,7 +65055,7 @@
       </c>
       <c r="B19" s="21" t="str">
         <f t="array" ref="B19">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B18,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,17),1,0),0)),"")</f>
-        <v>Alessio R.</v>
+        <v>Khawla</v>
       </c>
       <c r="C19" s="1">
         <f t="array" ref="C19">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B19,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65071,7 +65069,7 @@
       </c>
       <c r="B20" s="21" t="str">
         <f t="array" ref="B20">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B19,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,18),1,0),0)),"")</f>
-        <v>Marco P.</v>
+        <v>Federico R.</v>
       </c>
       <c r="C20" s="1">
         <f t="array" ref="C20">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B20,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65085,7 +65083,7 @@
       </c>
       <c r="B21" s="21" t="str">
         <f t="array" ref="B21">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B20,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,19),1,0),0)),"")</f>
-        <v>Khawla</v>
+        <v>Claudia S.</v>
       </c>
       <c r="C21" s="1">
         <f t="array" ref="C21">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B21,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65099,7 +65097,7 @@
       </c>
       <c r="B22" s="21" t="str">
         <f t="array" ref="B22">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B21,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,20),1,0),0)),"")</f>
-        <v>Federico R.</v>
+        <v>Leo Policella</v>
       </c>
       <c r="C22" s="1">
         <f t="array" ref="C22">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B22,Elenco!$B$5:$B$25,0)),"")</f>
@@ -65113,7 +65111,7 @@
       </c>
       <c r="B23" s="21" t="str">
         <f t="array" ref="B23">IFERROR(INDEX(Elenco!$B$5:$B$25,MATCH(0,COUNTIF($B$2:B22,Elenco!$B$5:$B$25)+IF(Elenco!$C$5:$C$25&lt;&gt;LARGE(Elenco!$C$5:$C$25,21),1,0),0)),"")</f>
-        <v>Leo Policella</v>
+        <v>Maila</v>
       </c>
       <c r="C23" s="1">
         <f t="array" ref="C23">IFERROR(INDEX(Elenco!$C$5:$C$25,MATCH(B23,Elenco!$B$5:$B$25,0)),"")</f>
